--- a/data/EAG/depolarizations.xlsx
+++ b/data/EAG/depolarizations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacksonstrand/Documents/GitHub/toadflax_hybrids_2026/data/EAG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31E58DE5-BBFA-954D-B4B2-7BD415FB4867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC6AD3B-10A3-B349-B78D-4C7B6EA9E8C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19660" xr2:uid="{C2DF0F49-E774-604A-A874-C69BEAC46AA2}"/>
+    <workbookView xWindow="-38400" yWindow="600" windowWidth="19200" windowHeight="21000" xr2:uid="{C2DF0F49-E774-604A-A874-C69BEAC46AA2}"/>
   </bookViews>
   <sheets>
     <sheet name="compound response" sheetId="1" r:id="rId1"/>
@@ -253,7 +253,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -282,6 +282,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -541,9 +544,9 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A0CD65AF-7D3D-064D-8A34-6087CB07AEA0}" name="Table1" displayName="Table1" ref="A1:M85" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27" tableBorderDxfId="26">
-  <autoFilter ref="A1:M85" xr:uid="{A0CD65AF-7D3D-064D-8A34-6087CB07AEA0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M85">
-    <sortCondition ref="B1:B85"/>
+    <sortCondition ref="C2:C85"/>
+    <sortCondition ref="A2:A85"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{4E4FD605-3AF7-E548-A827-FD5C531A0C97}" name="species" dataDxfId="25"/>
@@ -920,9 +923,9 @@
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11" style="2" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="14" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="11.33203125" style="3" customWidth="1"/>
     <col min="8" max="8" width="12.83203125" style="2" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" style="4"/>
@@ -977,7 +980,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>29</v>
@@ -986,251 +989,251 @@
         <v>11</v>
       </c>
       <c r="D2" s="2">
-        <v>0.86</v>
+        <v>0.31</v>
       </c>
       <c r="E2" s="3">
-        <f t="shared" ref="E2:E33" si="0">AVERAGE(I2:M2)</f>
-        <v>1.1519999999999997</v>
+        <f>AVERAGE(I2:M2)</f>
+        <v>0.13999999999999999</v>
       </c>
       <c r="F2" s="2">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="G2" s="3">
-        <f t="shared" ref="G2:G33" si="1">ROUND(STDEV(I2:M2)/SQRT(COUNT(I2:M2)),2)</f>
-        <v>0.26</v>
+        <f>ROUND(STDEV(I2:M2)/SQRT(COUNT(I2:M2)),2)</f>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H2" s="2">
         <v>5</v>
       </c>
       <c r="I2" s="4">
-        <v>1.22</v>
+        <v>0.03</v>
       </c>
       <c r="J2" s="2">
-        <v>1.92</v>
+        <v>0.18</v>
       </c>
       <c r="K2" s="2">
-        <v>0.51</v>
+        <v>0.1</v>
       </c>
       <c r="L2" s="2">
-        <v>0.68</v>
+        <v>0.38</v>
       </c>
       <c r="M2" s="2">
-        <v>1.43</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="2">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="E3" s="3">
-        <f t="shared" si="0"/>
-        <v>0.13999999999999999</v>
+        <f>AVERAGE(I3:M3)</f>
+        <v>0.312</v>
       </c>
       <c r="F3" s="2">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" si="1"/>
-        <v>7.0000000000000007E-2</v>
+        <f>ROUND(STDEV(I3:M3)/SQRT(COUNT(I3:M3)),2)</f>
+        <v>0.06</v>
       </c>
       <c r="H3" s="2">
         <v>5</v>
       </c>
       <c r="I3" s="4">
-        <v>0.03</v>
+        <v>0.18</v>
       </c>
       <c r="J3" s="2">
-        <v>0.18</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="K3" s="2">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="L3" s="2">
-        <v>0.38</v>
+        <v>0.21</v>
       </c>
       <c r="M3" s="2">
-        <v>0.01</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>9</v>
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
       </c>
       <c r="D4" s="2">
-        <v>3.2</v>
+        <v>0.34</v>
       </c>
       <c r="E4" s="3">
-        <f t="shared" si="0"/>
-        <v>3.3359999999999999</v>
+        <f>AVERAGE(I4:M4)</f>
+        <v>0.30399999999999999</v>
       </c>
       <c r="F4" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="G4" s="3">
+        <f>ROUND(STDEV(I4:M4)/SQRT(COUNT(I4:M4)),2)</f>
+        <v>0.08</v>
+      </c>
+      <c r="H4" s="2">
+        <v>5</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.39</v>
+      </c>
+      <c r="J4" s="2">
         <v>0.56000000000000005</v>
       </c>
-      <c r="G4" s="3">
-        <f t="shared" si="1"/>
-        <v>0.38</v>
-      </c>
-      <c r="H4" s="2">
-        <v>5</v>
-      </c>
-      <c r="I4" s="4">
-        <v>2.15</v>
-      </c>
-      <c r="J4" s="2">
-        <v>2.86</v>
-      </c>
       <c r="K4" s="2">
-        <v>3.9</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="L4" s="2">
-        <v>4.2699999999999996</v>
+        <v>0.16</v>
       </c>
       <c r="M4" s="2">
-        <v>3.5</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>9</v>
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
       </c>
       <c r="D5" s="2">
-        <v>5.94</v>
+        <v>0.41</v>
       </c>
       <c r="E5" s="3">
-        <f t="shared" si="0"/>
-        <v>7.5</v>
+        <f>AVERAGE(I5:M5)</f>
+        <v>0.52600000000000002</v>
       </c>
       <c r="F5" s="2">
-        <v>0.73</v>
+        <v>0.22</v>
       </c>
       <c r="G5" s="3">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <f>ROUND(STDEV(I5:M5)/SQRT(COUNT(I5:M5)),2)</f>
+        <v>0.05</v>
       </c>
       <c r="H5" s="2">
         <v>5</v>
       </c>
       <c r="I5" s="4">
-        <v>7.93</v>
+        <v>0.33</v>
       </c>
       <c r="J5" s="2">
-        <v>2.9</v>
+        <v>0.64</v>
       </c>
       <c r="K5" s="2">
-        <v>9.15</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="L5" s="2">
-        <v>9.6199999999999992</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M5" s="2">
-        <v>7.9</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D6" s="2">
-        <v>1.22</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E6" s="3">
-        <f t="shared" si="0"/>
-        <v>1.1739999999999999</v>
+        <f>AVERAGE(I6:M6)</f>
+        <v>0.25600000000000001</v>
       </c>
       <c r="F6" s="2">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="G6" s="3">
-        <f t="shared" si="1"/>
-        <v>0.1</v>
+        <f>ROUND(STDEV(I6:M6)/SQRT(COUNT(I6:M6)),2)</f>
+        <v>0.08</v>
       </c>
       <c r="H6" s="2">
         <v>5</v>
       </c>
       <c r="I6" s="4">
-        <v>1.18</v>
+        <v>0.51</v>
       </c>
       <c r="J6" s="2">
-        <v>1.1299999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="K6" s="2">
-        <v>1.1000000000000001</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="L6" s="2">
-        <v>1.55</v>
+        <v>0.34</v>
       </c>
       <c r="M6" s="2">
-        <v>0.91</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>7</v>
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
       </c>
       <c r="D7" s="2">
-        <v>1.31</v>
+        <v>0.21</v>
       </c>
       <c r="E7" s="3">
-        <f t="shared" si="0"/>
-        <v>1.5959999999999999</v>
+        <f>AVERAGE(I7:M7)</f>
+        <v>0.27600000000000002</v>
       </c>
       <c r="F7" s="2">
-        <v>0.34</v>
+        <v>0.12</v>
       </c>
       <c r="G7" s="3">
-        <f t="shared" si="1"/>
-        <v>0.34</v>
+        <f>ROUND(STDEV(I7:M7)/SQRT(COUNT(I7:M7)),2)</f>
+        <v>0.05</v>
       </c>
       <c r="H7" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7" s="4">
-        <v>1.08</v>
+        <v>0.15</v>
       </c>
       <c r="J7" s="2">
-        <v>1.26</v>
+        <v>0.23</v>
       </c>
       <c r="K7" s="2">
-        <v>2.85</v>
+        <v>0.42</v>
       </c>
       <c r="L7" s="2">
-        <v>1.78</v>
+        <v>0.25</v>
       </c>
       <c r="M7" s="2">
-        <v>1.01</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
@@ -1241,168 +1244,168 @@
         <v>29</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" s="2">
-        <v>2.11</v>
+        <v>0.86</v>
       </c>
       <c r="E8" s="3">
-        <f t="shared" si="0"/>
-        <v>2.1259999999999999</v>
+        <f>AVERAGE(I8:M8)</f>
+        <v>1.1519999999999997</v>
       </c>
       <c r="F8" s="2">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="G8" s="3">
-        <f t="shared" si="1"/>
-        <v>0.11</v>
+        <f>ROUND(STDEV(I8:M8)/SQRT(COUNT(I8:M8)),2)</f>
+        <v>0.26</v>
       </c>
       <c r="H8" s="2">
         <v>5</v>
       </c>
       <c r="I8" s="4">
-        <v>2.1</v>
+        <v>1.22</v>
       </c>
       <c r="J8" s="2">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="K8" s="2">
-        <v>2.08</v>
+        <v>0.51</v>
       </c>
       <c r="L8" s="2">
-        <v>1.77</v>
+        <v>0.68</v>
       </c>
       <c r="M8" s="2">
-        <v>2.4300000000000002</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>10</v>
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
       </c>
       <c r="D9" s="2">
-        <v>1.19</v>
+        <v>0.82</v>
       </c>
       <c r="E9" s="3">
-        <f t="shared" si="0"/>
-        <v>1.1099999999999999</v>
+        <f>AVERAGE(I9:M9)</f>
+        <v>1.0940000000000001</v>
       </c>
       <c r="F9" s="2">
-        <v>0.14000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="G9" s="3">
-        <f t="shared" si="1"/>
-        <v>0.17</v>
+        <f>ROUND(STDEV(I9:M9)/SQRT(COUNT(I9:M9)),2)</f>
+        <v>0.15</v>
       </c>
       <c r="H9" s="2">
         <v>5</v>
       </c>
       <c r="I9" s="4">
-        <v>1.21</v>
+        <v>0.73</v>
       </c>
       <c r="J9" s="2">
-        <v>0.63</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K9" s="2">
-        <v>0.9</v>
+        <v>1.22</v>
       </c>
       <c r="L9" s="2">
-        <v>1.1499999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="M9" s="2">
-        <v>1.66</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>5</v>
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
       </c>
       <c r="D10" s="2">
-        <v>3.14</v>
+        <v>0.22</v>
       </c>
       <c r="E10" s="3">
-        <f t="shared" si="0"/>
-        <v>3.048</v>
+        <f>AVERAGE(I10:M10)</f>
+        <v>0.22599999999999998</v>
       </c>
       <c r="F10" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="G10" s="3">
+        <f>ROUND(STDEV(I10:M10)/SQRT(COUNT(I10:M10)),2)</f>
+        <v>0.01</v>
+      </c>
+      <c r="H10" s="2">
+        <v>5</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.21</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.26</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="2">
         <v>0.31</v>
       </c>
-      <c r="G10" s="3">
-        <f t="shared" si="1"/>
-        <v>0.42</v>
-      </c>
-      <c r="H10" s="2">
-        <v>5</v>
-      </c>
-      <c r="I10" s="4">
-        <v>3.87</v>
-      </c>
-      <c r="J10" s="2">
-        <v>3.77</v>
-      </c>
-      <c r="K10" s="2">
-        <v>1.64</v>
-      </c>
-      <c r="L10" s="2">
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="M10" s="2">
-        <v>3.43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1.41</v>
-      </c>
       <c r="E11" s="3">
-        <f t="shared" si="0"/>
-        <v>1.516</v>
+        <f>AVERAGE(I11:M11)</f>
+        <v>0.67800000000000005</v>
       </c>
       <c r="F11" s="2">
-        <v>0.13</v>
+        <v>0.27</v>
       </c>
       <c r="G11" s="3">
-        <f t="shared" si="1"/>
-        <v>0.12</v>
+        <f>ROUND(STDEV(I11:M11)/SQRT(COUNT(I11:M11)),2)</f>
+        <v>0.18</v>
       </c>
       <c r="H11" s="2">
         <v>5</v>
       </c>
       <c r="I11" s="4">
-        <v>1.58</v>
+        <v>0.27</v>
       </c>
       <c r="J11" s="2">
-        <v>1.95</v>
+        <v>0.7</v>
       </c>
       <c r="K11" s="2">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="L11" s="2">
-        <v>1.41</v>
+        <v>0.33</v>
       </c>
       <c r="M11" s="2">
-        <v>1.39</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -1410,214 +1413,214 @@
         <v>16</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D12" s="2">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" si="0"/>
-        <v>0.30199999999999999</v>
+        <f>AVERAGE(I12:M12)</f>
+        <v>0.65000000000000013</v>
       </c>
       <c r="F12" s="2">
-        <v>0.01</v>
+        <v>0.59</v>
       </c>
       <c r="G12" s="3">
-        <f t="shared" si="1"/>
-        <v>0.01</v>
+        <f>ROUND(STDEV(I12:M12)/SQRT(COUNT(I12:M12)),2)</f>
+        <v>0.15</v>
       </c>
       <c r="H12" s="2">
         <v>5</v>
       </c>
       <c r="I12" s="4">
-        <v>0.3</v>
+        <v>1.17</v>
       </c>
       <c r="J12" s="2">
-        <v>0.31</v>
+        <v>0.39</v>
       </c>
       <c r="K12" s="2">
-        <v>0.28000000000000003</v>
+        <v>0.83</v>
       </c>
       <c r="L12" s="2">
-        <v>0.33</v>
+        <v>0.45</v>
       </c>
       <c r="M12" s="2">
-        <v>0.28999999999999998</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>8</v>
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
       </c>
       <c r="D13" s="2">
-        <v>0.55000000000000004</v>
+        <v>0.27</v>
       </c>
       <c r="E13" s="3">
-        <f t="shared" si="0"/>
-        <v>0.53400000000000003</v>
+        <f>AVERAGE(I13:M13)</f>
+        <v>0.23199999999999998</v>
       </c>
       <c r="F13" s="2">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="G13" s="3">
-        <f t="shared" si="1"/>
+        <f>ROUND(STDEV(I13:M13)/SQRT(COUNT(I13:M13)),2)</f>
         <v>0.03</v>
       </c>
       <c r="H13" s="2">
         <v>5</v>
       </c>
       <c r="I13" s="4">
-        <v>0.55000000000000004</v>
+        <v>0.13</v>
       </c>
       <c r="J13" s="2">
-        <v>0.47</v>
+        <v>0.23</v>
       </c>
       <c r="K13" s="2">
-        <v>0.55000000000000004</v>
+        <v>0.25</v>
       </c>
       <c r="L13" s="2">
-        <v>0.48</v>
+        <v>0.34</v>
       </c>
       <c r="M13" s="2">
-        <v>0.62</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2">
-        <v>2.12</v>
+        <v>5.94</v>
       </c>
       <c r="E14" s="3">
-        <f t="shared" si="0"/>
-        <v>2.2120000000000002</v>
+        <f>AVERAGE(I14:M14)</f>
+        <v>7.5</v>
       </c>
       <c r="F14" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.73</v>
       </c>
       <c r="G14" s="3">
-        <f t="shared" si="1"/>
-        <v>0.04</v>
+        <f>ROUND(STDEV(I14:M14)/SQRT(COUNT(I14:M14)),2)</f>
+        <v>1.2</v>
       </c>
       <c r="H14" s="2">
         <v>5</v>
       </c>
       <c r="I14" s="4">
-        <v>2.2599999999999998</v>
+        <v>7.93</v>
       </c>
       <c r="J14" s="2">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="K14" s="2">
-        <v>2.13</v>
+        <v>9.15</v>
       </c>
       <c r="L14" s="2">
-        <v>2.11</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="M14" s="2">
-        <v>2.25</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>6</v>
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>9</v>
       </c>
       <c r="D15" s="2">
-        <v>2.19</v>
+        <v>6.46</v>
       </c>
       <c r="E15" s="3">
-        <f t="shared" si="0"/>
-        <v>2.218</v>
+        <f>AVERAGE(I15:M15)</f>
+        <v>7.242</v>
       </c>
       <c r="F15" s="2">
-        <v>0.08</v>
+        <v>1.77</v>
       </c>
       <c r="G15" s="3">
-        <f t="shared" si="1"/>
-        <v>0.05</v>
+        <f>ROUND(STDEV(I15:M15)/SQRT(COUNT(I15:M15)),2)</f>
+        <v>1.05</v>
       </c>
       <c r="H15" s="2">
         <v>5</v>
       </c>
       <c r="I15" s="4">
-        <v>2.29</v>
+        <v>6.75</v>
       </c>
       <c r="J15" s="2">
-        <v>2.23</v>
+        <v>3.63</v>
       </c>
       <c r="K15" s="2">
-        <v>2.34</v>
+        <v>8.98</v>
       </c>
       <c r="L15" s="2">
-        <v>2.15</v>
+        <v>7.17</v>
       </c>
       <c r="M15" s="2">
-        <v>2.08</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2">
-        <v>0.82</v>
+        <v>7.9</v>
       </c>
       <c r="E16" s="3">
-        <f t="shared" si="0"/>
-        <v>1.0940000000000001</v>
+        <f>AVERAGE(I16:M16)</f>
+        <v>6.3280000000000003</v>
       </c>
       <c r="F16" s="2">
-        <v>0.19</v>
+        <v>0.32</v>
       </c>
       <c r="G16" s="3">
-        <f t="shared" si="1"/>
-        <v>0.15</v>
+        <f>ROUND(STDEV(I16:M16)/SQRT(COUNT(I16:M16)),2)</f>
+        <v>0.49</v>
       </c>
       <c r="H16" s="2">
         <v>5</v>
       </c>
       <c r="I16" s="4">
-        <v>0.73</v>
+        <v>6.1</v>
       </c>
       <c r="J16" s="2">
-        <v>1.1000000000000001</v>
+        <v>7.28</v>
       </c>
       <c r="K16" s="2">
-        <v>1.22</v>
+        <v>6.9</v>
       </c>
       <c r="L16" s="2">
-        <v>1.6</v>
+        <v>4.53</v>
       </c>
       <c r="M16" s="2">
-        <v>0.82</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
@@ -1625,85 +1628,85 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2">
+        <v>5.67</v>
+      </c>
+      <c r="E17" s="3">
+        <f>AVERAGE(I17:M17)</f>
+        <v>5.3179999999999996</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G17" s="3">
+        <f>ROUND(STDEV(I17:M17)/SQRT(COUNT(I17:M17)),2)</f>
+        <v>0.26</v>
+      </c>
+      <c r="H17" s="2">
+        <v>5</v>
+      </c>
+      <c r="I17" s="4">
+        <v>6.27</v>
+      </c>
+      <c r="J17" s="2">
+        <v>4.95</v>
+      </c>
+      <c r="K17" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="L17" s="2">
+        <v>5.17</v>
+      </c>
+      <c r="M17" s="2">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2">
+        <v>5.19</v>
+      </c>
+      <c r="E18" s="3">
+        <f>AVERAGE(I18:M18)</f>
+        <v>4.9539999999999988</v>
+      </c>
+      <c r="F18" s="2">
         <v>0.32</v>
       </c>
-      <c r="E17" s="3">
-        <f t="shared" si="0"/>
-        <v>0.312</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="G17" s="3">
-        <f t="shared" si="1"/>
-        <v>0.06</v>
-      </c>
-      <c r="H17" s="2">
-        <v>5</v>
-      </c>
-      <c r="I17" s="4">
-        <v>0.18</v>
-      </c>
-      <c r="J17" s="2">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="K17" s="2">
-        <v>0.36</v>
-      </c>
-      <c r="L17" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="M17" s="2">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2">
+      <c r="G18" s="3">
+        <f>ROUND(STDEV(I18:M18)/SQRT(COUNT(I18:M18)),2)</f>
+        <v>0.48</v>
+      </c>
+      <c r="H18" s="2">
+        <v>5</v>
+      </c>
+      <c r="I18" s="4">
+        <v>5.33</v>
+      </c>
+      <c r="J18" s="2">
+        <v>5.23</v>
+      </c>
+      <c r="K18" s="2">
         <v>5.98</v>
       </c>
-      <c r="E18" s="3">
-        <f t="shared" si="0"/>
-        <v>3.7640000000000002</v>
-      </c>
-      <c r="F18" s="2">
-        <v>1.42</v>
-      </c>
-      <c r="G18" s="3">
-        <f t="shared" si="1"/>
-        <v>0.9</v>
-      </c>
-      <c r="H18" s="2">
-        <v>5</v>
-      </c>
-      <c r="I18" s="4">
-        <v>5.36</v>
-      </c>
-      <c r="J18" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="K18" s="2">
-        <v>5.93</v>
-      </c>
       <c r="L18" s="2">
-        <v>1.74</v>
-      </c>
-      <c r="M18" s="2">
-        <v>4.1900000000000004</v>
+        <v>3.15</v>
+      </c>
+      <c r="M18" s="12">
+        <v>5.08</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
@@ -1711,128 +1714,128 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="2">
-        <v>6.46</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="E19" s="3">
-        <f t="shared" si="0"/>
-        <v>7.242</v>
+        <f>AVERAGE(I19:M19)</f>
+        <v>4.3339999999999996</v>
       </c>
       <c r="F19" s="2">
-        <v>1.77</v>
+        <v>0.12</v>
       </c>
       <c r="G19" s="3">
-        <f t="shared" si="1"/>
-        <v>1.05</v>
+        <f>ROUND(STDEV(I19:M19)/SQRT(COUNT(I19:M19)),2)</f>
+        <v>0.08</v>
       </c>
       <c r="H19" s="2">
         <v>5</v>
       </c>
       <c r="I19" s="4">
-        <v>6.75</v>
+        <v>4.58</v>
       </c>
       <c r="J19" s="2">
-        <v>3.63</v>
+        <v>4.17</v>
       </c>
       <c r="K19" s="2">
-        <v>8.98</v>
+        <v>4.41</v>
       </c>
       <c r="L19" s="2">
-        <v>7.17</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="M19" s="2">
-        <v>9.68</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" t="s">
-        <v>7</v>
+      <c r="A20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="D20" s="2">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="E20" s="3">
-        <f t="shared" si="0"/>
-        <v>1.024</v>
+        <f>AVERAGE(I20:M20)</f>
+        <v>3.3359999999999999</v>
       </c>
       <c r="F20" s="2">
-        <v>0.11</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="G20" s="3">
-        <f t="shared" si="1"/>
-        <v>0.06</v>
+        <f>ROUND(STDEV(I20:M20)/SQRT(COUNT(I20:M20)),2)</f>
+        <v>0.38</v>
       </c>
       <c r="H20" s="2">
         <v>5</v>
       </c>
       <c r="I20" s="4">
-        <v>0.82</v>
+        <v>2.15</v>
       </c>
       <c r="J20" s="2">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="K20" s="2">
-        <v>1.22</v>
+        <v>3.9</v>
       </c>
       <c r="L20" s="2">
-        <v>1</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="M20" s="2">
-        <v>1.05</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
         <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2">
-        <v>1.21</v>
+        <v>5.98</v>
       </c>
       <c r="E21" s="3">
-        <f t="shared" si="0"/>
-        <v>0.99599999999999989</v>
+        <f>AVERAGE(I21:M21)</f>
+        <v>3.7640000000000002</v>
       </c>
       <c r="F21" s="2">
-        <v>0.31</v>
+        <v>1.42</v>
       </c>
       <c r="G21" s="3">
-        <f t="shared" si="1"/>
-        <v>0.32</v>
+        <f>ROUND(STDEV(I21:M21)/SQRT(COUNT(I21:M21)),2)</f>
+        <v>0.9</v>
       </c>
       <c r="H21" s="2">
         <v>5</v>
       </c>
       <c r="I21" s="4">
-        <v>1.18</v>
+        <v>5.36</v>
       </c>
       <c r="J21" s="2">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="K21" s="2">
-        <v>0.32</v>
+        <v>5.93</v>
       </c>
       <c r="L21" s="2">
-        <v>0.15</v>
+        <v>1.74</v>
       </c>
       <c r="M21" s="2">
-        <v>1.7</v>
+        <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
@@ -1840,214 +1843,214 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2">
-        <v>1.76</v>
+        <v>4.5</v>
       </c>
       <c r="E22" s="3">
-        <f t="shared" si="0"/>
-        <v>1.6920000000000002</v>
+        <f>AVERAGE(I22:M22)</f>
+        <v>4.702</v>
       </c>
       <c r="F22" s="2">
-        <v>0.67</v>
+        <v>0.13</v>
       </c>
       <c r="G22" s="3">
-        <f t="shared" si="1"/>
-        <v>0.57999999999999996</v>
+        <f>ROUND(STDEV(I22:M22)/SQRT(COUNT(I22:M22)),2)</f>
+        <v>0.18</v>
       </c>
       <c r="H22" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I22" s="4">
-        <v>0.39</v>
+        <v>4.57</v>
       </c>
       <c r="J22" s="2">
-        <v>1.0900000000000001</v>
+        <v>4.92</v>
       </c>
       <c r="K22" s="2">
-        <v>3.81</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="L22" s="2">
-        <v>1.78</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="M22" s="5">
-        <v>1.39</v>
+        <v>4.9000000000000004</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2">
-        <v>1.07</v>
+        <v>4.3</v>
       </c>
       <c r="E23" s="3">
-        <f t="shared" si="0"/>
-        <v>1.1579999999999999</v>
+        <f>AVERAGE(I23:M23)</f>
+        <v>4.0600000000000005</v>
       </c>
       <c r="F23" s="2">
-        <v>0.05</v>
+        <v>0.31</v>
       </c>
       <c r="G23" s="3">
-        <f t="shared" si="1"/>
-        <v>0.03</v>
+        <f>ROUND(STDEV(I23:M23)/SQRT(COUNT(I23:M23)),2)</f>
+        <v>0.09</v>
       </c>
       <c r="H23" s="2">
         <v>5</v>
       </c>
       <c r="I23" s="4">
-        <v>1.1599999999999999</v>
+        <v>3.84</v>
       </c>
       <c r="J23" s="2">
-        <v>1.1000000000000001</v>
+        <v>4.01</v>
       </c>
       <c r="K23" s="2">
-        <v>1.08</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="L23" s="2">
-        <v>1.23</v>
+        <v>4.29</v>
       </c>
       <c r="M23" s="5">
-        <v>1.22</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" t="s">
-        <v>5</v>
+      <c r="A24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="D24" s="2">
-        <v>2.77</v>
+        <v>6.15</v>
       </c>
       <c r="E24" s="3">
-        <f t="shared" si="0"/>
-        <v>4.016</v>
+        <f>AVERAGE(I24:M24)</f>
+        <v>5.9320000000000004</v>
       </c>
       <c r="F24" s="2">
-        <v>0.74</v>
+        <v>0.48</v>
       </c>
       <c r="G24" s="3">
-        <f t="shared" si="1"/>
-        <v>0.47</v>
+        <f>ROUND(STDEV(I24:M24)/SQRT(COUNT(I24:M24)),2)</f>
+        <v>0.19</v>
       </c>
       <c r="H24" s="2">
         <v>5</v>
       </c>
       <c r="I24" s="4">
-        <v>5.2</v>
+        <v>6.28</v>
       </c>
       <c r="J24" s="2">
-        <v>2.78</v>
+        <v>6.29</v>
       </c>
       <c r="K24" s="2">
-        <v>3.87</v>
+        <v>5.23</v>
       </c>
       <c r="L24" s="2">
-        <v>3.29</v>
-      </c>
-      <c r="M24" s="2">
-        <v>4.9400000000000004</v>
+        <v>5.96</v>
+      </c>
+      <c r="M24" s="12">
+        <v>5.9</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2">
-        <v>1.32</v>
+        <v>7.2</v>
       </c>
       <c r="E25" s="3">
-        <f t="shared" si="0"/>
-        <v>1.532</v>
+        <f>AVERAGE(I25:M25)</f>
+        <v>7.1059999999999999</v>
       </c>
       <c r="F25" s="2">
-        <v>0.19</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="G25" s="3">
-        <f t="shared" si="1"/>
-        <v>0.19</v>
+        <f>ROUND(STDEV(I25:M25)/SQRT(COUNT(I25:M25)),2)</f>
+        <v>1.63</v>
       </c>
       <c r="H25" s="2">
         <v>5</v>
       </c>
       <c r="I25" s="4">
-        <v>2.19</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="J25" s="2">
-        <v>1.36</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="K25" s="2">
-        <v>1.02</v>
+        <v>9.6</v>
       </c>
       <c r="L25" s="2">
-        <v>1.64</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="M25" s="2">
-        <v>1.45</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" t="s">
-        <v>8</v>
+      <c r="A26" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="D26" s="2">
-        <v>0.27</v>
+        <v>1.31</v>
       </c>
       <c r="E26" s="3">
-        <f t="shared" si="0"/>
-        <v>0.246</v>
+        <f>AVERAGE(I26:M26)</f>
+        <v>1.5959999999999999</v>
       </c>
       <c r="F26" s="2">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
       <c r="G26" s="3">
-        <f t="shared" si="1"/>
-        <v>0.08</v>
+        <f>ROUND(STDEV(I26:M26)/SQRT(COUNT(I26:M26)),2)</f>
+        <v>0.34</v>
       </c>
       <c r="H26" s="2">
         <v>5</v>
       </c>
       <c r="I26" s="4">
-        <v>0.25</v>
+        <v>1.08</v>
       </c>
       <c r="J26" s="2">
-        <v>0.55000000000000004</v>
+        <v>1.26</v>
       </c>
       <c r="K26" s="2">
-        <v>0.19</v>
+        <v>2.85</v>
       </c>
       <c r="L26" s="2">
-        <v>0.09</v>
+        <v>1.78</v>
       </c>
       <c r="M26" s="2">
-        <v>0.15</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
@@ -2058,82 +2061,82 @@
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D27" s="2">
-        <v>0.42</v>
+        <v>1.21</v>
       </c>
       <c r="E27" s="3">
-        <f t="shared" si="0"/>
-        <v>0.7340000000000001</v>
+        <f>AVERAGE(I27:M27)</f>
+        <v>0.99599999999999989</v>
       </c>
       <c r="F27" s="2">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="G27" s="3">
-        <f t="shared" si="1"/>
-        <v>0.17</v>
+        <f>ROUND(STDEV(I27:M27)/SQRT(COUNT(I27:M27)),2)</f>
+        <v>0.32</v>
       </c>
       <c r="H27" s="2">
         <v>5</v>
       </c>
       <c r="I27" s="4">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="J27" s="2">
-        <v>0.8</v>
+        <v>1.63</v>
       </c>
       <c r="K27" s="2">
-        <v>0.11</v>
+        <v>0.32</v>
       </c>
       <c r="L27" s="2">
-        <v>0.7</v>
+        <v>0.15</v>
       </c>
       <c r="M27" s="2">
-        <v>1.06</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" s="2">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="E28" s="3">
-        <f t="shared" si="0"/>
-        <v>1.6600000000000001</v>
+        <f>AVERAGE(I28:M28)</f>
+        <v>0.95399999999999996</v>
       </c>
       <c r="F28" s="2">
-        <v>0.55000000000000004</v>
+        <v>0.22</v>
       </c>
       <c r="G28" s="3">
-        <f t="shared" si="1"/>
-        <v>0.53</v>
+        <f>ROUND(STDEV(I28:M28)/SQRT(COUNT(I28:M28)),2)</f>
+        <v>0.32</v>
       </c>
       <c r="H28" s="2">
         <v>5</v>
       </c>
       <c r="I28" s="4">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="J28" s="2">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="K28" s="2">
-        <v>3.38</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="L28" s="2">
-        <v>2.08</v>
+        <v>0.61</v>
       </c>
       <c r="M28" s="2">
-        <v>1.76</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
@@ -2141,85 +2144,85 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" s="2">
-        <v>2.0099999999999998</v>
+        <v>1.57</v>
       </c>
       <c r="E29" s="3">
-        <f t="shared" si="0"/>
-        <v>2.1259999999999999</v>
+        <f>AVERAGE(I29:M29)</f>
+        <v>1.488</v>
       </c>
       <c r="F29" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="G29" s="3">
+        <f>ROUND(STDEV(I29:M29)/SQRT(COUNT(I29:M29)),2)</f>
         <v>0.22</v>
       </c>
-      <c r="G29" s="3">
-        <f t="shared" si="1"/>
-        <v>0.28000000000000003</v>
-      </c>
       <c r="H29" s="2">
         <v>5</v>
       </c>
       <c r="I29" s="4">
-        <v>2.73</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="J29" s="2">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="K29" s="2">
-        <v>2.52</v>
+        <v>0.8</v>
       </c>
       <c r="L29" s="2">
-        <v>2.4300000000000002</v>
+        <v>1.43</v>
       </c>
       <c r="M29" s="2">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" t="s">
-        <v>11</v>
+      <c r="A30" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="D30" s="2">
-        <v>0.22</v>
+        <v>0.59</v>
       </c>
       <c r="E30" s="3">
-        <f t="shared" si="0"/>
-        <v>0.22599999999999998</v>
+        <f>AVERAGE(I30:M30)</f>
+        <v>0.45199999999999996</v>
       </c>
       <c r="F30" s="2">
-        <v>0.01</v>
+        <v>0.24</v>
       </c>
       <c r="G30" s="3">
-        <f t="shared" si="1"/>
-        <v>0.01</v>
+        <f>ROUND(STDEV(I30:M30)/SQRT(COUNT(I30:M30)),2)</f>
+        <v>0.25</v>
       </c>
       <c r="H30" s="2">
         <v>5</v>
       </c>
       <c r="I30" s="4">
-        <v>0.21</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="J30" s="2">
-        <v>0.26</v>
+        <v>1.41</v>
       </c>
       <c r="K30" s="2">
-        <v>0.23</v>
+        <v>0.11</v>
       </c>
       <c r="L30" s="2">
-        <v>0.2</v>
+        <v>0.42</v>
       </c>
       <c r="M30" s="2">
-        <v>0.23</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
@@ -2227,128 +2230,128 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D31" s="2">
-        <v>0.34</v>
+        <v>0.64</v>
       </c>
       <c r="E31" s="3">
-        <f t="shared" si="0"/>
-        <v>0.30399999999999999</v>
+        <f>AVERAGE(I31:M31)</f>
+        <v>0.78999999999999992</v>
       </c>
       <c r="F31" s="2">
-        <v>0.12</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G31" s="3">
-        <f t="shared" si="1"/>
-        <v>0.08</v>
+        <f>ROUND(STDEV(I31:M31)/SQRT(COUNT(I31:M31)),2)</f>
+        <v>0.09</v>
       </c>
       <c r="H31" s="2">
         <v>5</v>
       </c>
       <c r="I31" s="4">
-        <v>0.39</v>
+        <v>0.94</v>
       </c>
       <c r="J31" s="2">
-        <v>0.56000000000000005</v>
+        <v>1.04</v>
       </c>
       <c r="K31" s="2">
-        <v>0.28999999999999998</v>
+        <v>0.73</v>
       </c>
       <c r="L31" s="2">
-        <v>0.16</v>
+        <v>0.59</v>
       </c>
       <c r="M31" s="2">
-        <v>0.12</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>16</v>
-      </c>
-      <c r="B32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C32" t="s">
-        <v>9</v>
+      <c r="A32" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="D32" s="2">
-        <v>4.5</v>
+        <v>1.22</v>
       </c>
       <c r="E32" s="3">
-        <f t="shared" si="0"/>
-        <v>4.702</v>
+        <f>AVERAGE(I32:M32)</f>
+        <v>1.1739999999999999</v>
       </c>
       <c r="F32" s="2">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="G32" s="3">
-        <f t="shared" si="1"/>
-        <v>0.18</v>
+        <f>ROUND(STDEV(I32:M32)/SQRT(COUNT(I32:M32)),2)</f>
+        <v>0.1</v>
       </c>
       <c r="H32" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I32" s="4">
-        <v>4.57</v>
+        <v>1.18</v>
       </c>
       <c r="J32" s="2">
-        <v>4.92</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="K32" s="2">
-        <v>4.0599999999999996</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L32" s="2">
-        <v>5.0599999999999996</v>
+        <v>1.55</v>
       </c>
       <c r="M32" s="2">
-        <v>4.9000000000000004</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D33" s="2">
-        <v>7.9</v>
+        <v>1.01</v>
       </c>
       <c r="E33" s="3">
-        <f t="shared" si="0"/>
-        <v>6.3280000000000003</v>
+        <f>AVERAGE(I33:M33)</f>
+        <v>1.024</v>
       </c>
       <c r="F33" s="2">
-        <v>0.32</v>
+        <v>0.11</v>
       </c>
       <c r="G33" s="3">
-        <f t="shared" si="1"/>
-        <v>0.49</v>
+        <f>ROUND(STDEV(I33:M33)/SQRT(COUNT(I33:M33)),2)</f>
+        <v>0.06</v>
       </c>
       <c r="H33" s="2">
         <v>5</v>
       </c>
       <c r="I33" s="4">
-        <v>6.1</v>
+        <v>0.82</v>
       </c>
       <c r="J33" s="2">
-        <v>7.28</v>
+        <v>1.03</v>
       </c>
       <c r="K33" s="2">
-        <v>6.9</v>
+        <v>1.22</v>
       </c>
       <c r="L33" s="2">
-        <v>4.53</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2">
-        <v>6.83</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
@@ -2365,14 +2368,14 @@
         <v>1.8</v>
       </c>
       <c r="E34" s="3">
-        <f t="shared" ref="E34:E65" si="2">AVERAGE(I34:M34)</f>
+        <f>AVERAGE(I34:M34)</f>
         <v>1.8359999999999999</v>
       </c>
       <c r="F34" s="2">
         <v>0.33</v>
       </c>
       <c r="G34" s="3">
-        <f t="shared" ref="G34:G65" si="3">ROUND(STDEV(I34:M34)/SQRT(COUNT(I34:M34)),2)</f>
+        <f>ROUND(STDEV(I34:M34)/SQRT(COUNT(I34:M34)),2)</f>
         <v>0.37</v>
       </c>
       <c r="H34" s="2">
@@ -2396,174 +2399,174 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C35" t="s">
         <v>7</v>
       </c>
       <c r="D35" s="2">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="E35" s="3">
-        <f t="shared" si="2"/>
-        <v>0.95399999999999996</v>
+        <f>AVERAGE(I35:M35)</f>
+        <v>1.238</v>
       </c>
       <c r="F35" s="2">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="G35" s="3">
-        <f t="shared" si="3"/>
-        <v>0.32</v>
+        <f>ROUND(STDEV(I35:M35)/SQRT(COUNT(I35:M35)),2)</f>
+        <v>0.17</v>
       </c>
       <c r="H35" s="2">
         <v>5</v>
       </c>
       <c r="I35" s="4">
-        <v>0.6</v>
+        <v>1.05</v>
       </c>
       <c r="J35" s="2">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="K35" s="2">
-        <v>2.2400000000000002</v>
+        <v>1.81</v>
       </c>
       <c r="L35" s="2">
-        <v>0.61</v>
+        <v>1.39</v>
       </c>
       <c r="M35" s="2">
-        <v>0.52</v>
+        <v>1.1100000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>16</v>
-      </c>
-      <c r="B36" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" t="s">
-        <v>10</v>
+      <c r="A36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="D36" s="2">
-        <v>3.55</v>
+        <v>1.95</v>
       </c>
       <c r="E36" s="3">
-        <f t="shared" si="2"/>
-        <v>4.1100000000000003</v>
+        <f>AVERAGE(I36:M36)</f>
+        <v>1.6719999999999999</v>
       </c>
       <c r="F36" s="2">
-        <v>1.06</v>
+        <v>0.2</v>
       </c>
       <c r="G36" s="3">
-        <f t="shared" si="3"/>
-        <v>1.04</v>
+        <f>ROUND(STDEV(I36:M36)/SQRT(COUNT(I36:M36)),2)</f>
+        <v>0.19</v>
       </c>
       <c r="H36" s="2">
         <v>5</v>
       </c>
       <c r="I36" s="4">
-        <v>2.63</v>
+        <v>0.92</v>
       </c>
       <c r="J36" s="2">
-        <v>4.24</v>
+        <v>2</v>
       </c>
       <c r="K36" s="2">
-        <v>5.54</v>
+        <v>1.69</v>
       </c>
       <c r="L36" s="2">
-        <v>7.03</v>
+        <v>1.84</v>
       </c>
       <c r="M36" s="2">
-        <v>1.1100000000000001</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B37" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="2">
+        <v>1.77</v>
+      </c>
+      <c r="E37" s="3">
+        <f>AVERAGE(I37:M37)</f>
+        <v>1.6440000000000001</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="G37" s="3">
+        <f>ROUND(STDEV(I37:M37)/SQRT(COUNT(I37:M37)),2)</f>
+        <v>0.17</v>
+      </c>
+      <c r="H37" s="2">
+        <v>5</v>
+      </c>
+      <c r="I37" s="4">
+        <v>2.21</v>
+      </c>
+      <c r="J37" s="2">
+        <v>1.36</v>
+      </c>
+      <c r="K37" s="2">
+        <v>1.64</v>
+      </c>
+      <c r="L37" s="2">
+        <v>1.79</v>
+      </c>
+      <c r="M37" s="2">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="E37" s="3">
-        <f t="shared" si="2"/>
-        <v>1.284</v>
-      </c>
-      <c r="F37" s="2">
-        <v>0.33</v>
-      </c>
-      <c r="G37" s="3">
-        <f t="shared" si="3"/>
-        <v>0.22</v>
-      </c>
-      <c r="H37" s="2">
-        <v>5</v>
-      </c>
-      <c r="I37" s="4">
-        <v>1.39</v>
-      </c>
-      <c r="J37" s="2">
-        <v>1.91</v>
-      </c>
-      <c r="K37" s="2">
-        <v>1.47</v>
-      </c>
-      <c r="L37" s="2">
-        <v>0.62</v>
-      </c>
-      <c r="M37" s="2">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>16</v>
-      </c>
-      <c r="B38" t="s">
-        <v>27</v>
-      </c>
-      <c r="C38" t="s">
-        <v>5</v>
-      </c>
       <c r="D38" s="2">
-        <v>3.15</v>
+        <v>1.19</v>
       </c>
       <c r="E38" s="3">
-        <f t="shared" si="2"/>
-        <v>2.9180000000000001</v>
+        <f>AVERAGE(I38:M38)</f>
+        <v>1.1099999999999999</v>
       </c>
       <c r="F38" s="2">
-        <v>0.43</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G38" s="3">
-        <f t="shared" si="3"/>
-        <v>0.54</v>
+        <f>ROUND(STDEV(I38:M38)/SQRT(COUNT(I38:M38)),2)</f>
+        <v>0.17</v>
       </c>
       <c r="H38" s="2">
         <v>5</v>
       </c>
       <c r="I38" s="4">
-        <v>2.66</v>
+        <v>1.21</v>
       </c>
       <c r="J38" s="2">
-        <v>3.98</v>
+        <v>0.63</v>
       </c>
       <c r="K38" s="2">
-        <v>4.38</v>
+        <v>0.9</v>
       </c>
       <c r="L38" s="2">
-        <v>1.9</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="M38" s="2">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
@@ -2571,85 +2574,85 @@
         <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D39" s="2">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="E39" s="3">
-        <f t="shared" si="2"/>
-        <v>1.5680000000000001</v>
+        <f>AVERAGE(I39:M39)</f>
+        <v>1.1579999999999999</v>
       </c>
       <c r="F39" s="2">
-        <v>0.31</v>
+        <v>0.05</v>
       </c>
       <c r="G39" s="3">
-        <f t="shared" si="3"/>
-        <v>0.22</v>
+        <f>ROUND(STDEV(I39:M39)/SQRT(COUNT(I39:M39)),2)</f>
+        <v>0.03</v>
       </c>
       <c r="H39" s="2">
         <v>5</v>
       </c>
       <c r="I39" s="4">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="J39" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K39" s="2">
+        <v>1.08</v>
+      </c>
+      <c r="L39" s="2">
+        <v>1.23</v>
+      </c>
+      <c r="M39" s="12">
         <v>1.22</v>
-      </c>
-      <c r="J39" s="2">
-        <v>2.02</v>
-      </c>
-      <c r="K39" s="2">
-        <v>2.16</v>
-      </c>
-      <c r="L39" s="2">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="M39" s="2">
-        <v>1.32</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B40" t="s">
         <v>27</v>
       </c>
       <c r="C40" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D40" s="2">
-        <v>0.24</v>
+        <v>1.5</v>
       </c>
       <c r="E40" s="3">
-        <f t="shared" si="2"/>
-        <v>0.23199999999999998</v>
+        <f>AVERAGE(I40:M40)</f>
+        <v>1.284</v>
       </c>
       <c r="F40" s="2">
-        <v>0.05</v>
+        <v>0.33</v>
       </c>
       <c r="G40" s="3">
-        <f t="shared" si="3"/>
-        <v>0.04</v>
+        <f>ROUND(STDEV(I40:M40)/SQRT(COUNT(I40:M40)),2)</f>
+        <v>0.22</v>
       </c>
       <c r="H40" s="2">
         <v>5</v>
       </c>
       <c r="I40" s="4">
-        <v>0.3</v>
+        <v>1.39</v>
       </c>
       <c r="J40" s="2">
-        <v>0.34</v>
+        <v>1.91</v>
       </c>
       <c r="K40" s="2">
-        <v>0.24</v>
+        <v>1.47</v>
       </c>
       <c r="L40" s="2">
-        <v>0.13</v>
+        <v>0.62</v>
       </c>
       <c r="M40" s="2">
-        <v>0.15</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
@@ -2657,85 +2660,85 @@
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C41" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D41" s="2">
-        <v>0.75</v>
+        <v>1.77</v>
       </c>
       <c r="E41" s="3">
-        <f t="shared" si="2"/>
-        <v>0.81199999999999994</v>
+        <f>AVERAGE(I41:M41)</f>
+        <v>1.6280000000000001</v>
       </c>
       <c r="F41" s="2">
-        <v>0.11</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G41" s="3">
-        <f t="shared" si="3"/>
-        <v>0.12</v>
+        <f>ROUND(STDEV(I41:M41)/SQRT(COUNT(I41:M41)),2)</f>
+        <v>0.39</v>
       </c>
       <c r="H41" s="2">
         <v>5</v>
       </c>
       <c r="I41" s="4">
-        <v>0.97</v>
+        <v>1.45</v>
       </c>
       <c r="J41" s="2">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="K41" s="2">
-        <v>0.66</v>
+        <v>0.94</v>
       </c>
       <c r="L41" s="2">
-        <v>1.17</v>
+        <v>0.72</v>
       </c>
       <c r="M41" s="2">
-        <v>0.76</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>16</v>
-      </c>
-      <c r="B42" t="s">
-        <v>27</v>
-      </c>
-      <c r="C42" t="s">
-        <v>6</v>
+      <c r="A42" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="D42" s="2">
-        <v>4.3</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="E42" s="3">
-        <f t="shared" si="2"/>
-        <v>3.9159999999999995</v>
+        <f>AVERAGE(I42:M42)</f>
+        <v>1.1919999999999999</v>
       </c>
       <c r="F42" s="2">
-        <v>1.07</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G42" s="3">
-        <f t="shared" si="3"/>
-        <v>0.85</v>
+        <f>ROUND(STDEV(I42:M42)/SQRT(COUNT(I42:M42)),2)</f>
+        <v>0.05</v>
       </c>
       <c r="H42" s="2">
         <v>5</v>
       </c>
       <c r="I42" s="4">
-        <v>2.7</v>
+        <v>1.06</v>
       </c>
       <c r="J42" s="2">
-        <v>2.74</v>
+        <v>1.18</v>
       </c>
       <c r="K42" s="2">
-        <v>6.38</v>
+        <v>1.25</v>
       </c>
       <c r="L42" s="2">
-        <v>5.56</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="M42" s="2">
-        <v>2.2000000000000002</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
@@ -2743,128 +2746,128 @@
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C43" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D43" s="2">
-        <v>3.1</v>
+        <v>0.82</v>
       </c>
       <c r="E43" s="3">
-        <f t="shared" si="2"/>
-        <v>3.5020000000000002</v>
+        <f>AVERAGE(I43:M43)</f>
+        <v>0.57800000000000007</v>
       </c>
       <c r="F43" s="2">
-        <v>0.54</v>
+        <v>0.11</v>
       </c>
       <c r="G43" s="3">
-        <f t="shared" si="3"/>
-        <v>0.66</v>
+        <f>ROUND(STDEV(I43:M43)/SQRT(COUNT(I43:M43)),2)</f>
+        <v>0.09</v>
       </c>
       <c r="H43" s="2">
         <v>5</v>
       </c>
       <c r="I43" s="4">
-        <v>3.77</v>
+        <v>0.76</v>
       </c>
       <c r="J43" s="2">
-        <v>1.76</v>
+        <v>0.8</v>
       </c>
       <c r="K43" s="2">
-        <v>2.36</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L43" s="2">
-        <v>4.1399999999999997</v>
+        <v>0.4</v>
       </c>
       <c r="M43" s="2">
-        <v>5.48</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>16</v>
-      </c>
-      <c r="B44" t="s">
-        <v>28</v>
-      </c>
-      <c r="C44" t="s">
-        <v>11</v>
+      <c r="A44" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="D44" s="2">
-        <v>0.31</v>
+        <v>2.11</v>
       </c>
       <c r="E44" s="3">
-        <f t="shared" si="2"/>
-        <v>0.67800000000000005</v>
+        <f>AVERAGE(I44:M44)</f>
+        <v>2.1259999999999999</v>
       </c>
       <c r="F44" s="2">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="G44" s="3">
-        <f t="shared" si="3"/>
-        <v>0.18</v>
+        <f>ROUND(STDEV(I44:M44)/SQRT(COUNT(I44:M44)),2)</f>
+        <v>0.11</v>
       </c>
       <c r="H44" s="2">
         <v>5</v>
       </c>
       <c r="I44" s="4">
-        <v>0.27</v>
+        <v>2.1</v>
       </c>
       <c r="J44" s="2">
-        <v>0.7</v>
+        <v>2.25</v>
       </c>
       <c r="K44" s="2">
-        <v>1.28</v>
+        <v>2.08</v>
       </c>
       <c r="L44" s="2">
-        <v>0.33</v>
+        <v>1.77</v>
       </c>
       <c r="M44" s="2">
-        <v>0.81</v>
+        <v>2.4300000000000002</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D45" s="2">
-        <v>0.41</v>
+        <v>1.76</v>
       </c>
       <c r="E45" s="3">
-        <f t="shared" si="2"/>
-        <v>0.52600000000000002</v>
+        <f>AVERAGE(I45:M45)</f>
+        <v>1.6920000000000002</v>
       </c>
       <c r="F45" s="2">
-        <v>0.22</v>
+        <v>0.67</v>
       </c>
       <c r="G45" s="3">
-        <f t="shared" si="3"/>
-        <v>0.05</v>
+        <f>ROUND(STDEV(I45:M45)/SQRT(COUNT(I45:M45)),2)</f>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H45" s="2">
         <v>5</v>
       </c>
       <c r="I45" s="4">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="J45" s="2">
-        <v>0.64</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="K45" s="2">
-        <v>0.56999999999999995</v>
+        <v>3.81</v>
       </c>
       <c r="L45" s="2">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="M45" s="2">
-        <v>0.53</v>
+        <v>1.78</v>
+      </c>
+      <c r="M45" s="12">
+        <v>1.39</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
@@ -2872,214 +2875,214 @@
         <v>16</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D46" s="2">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="E46" s="3">
-        <f t="shared" si="2"/>
-        <v>4.0600000000000005</v>
+        <f>AVERAGE(I46:M46)</f>
+        <v>4.1100000000000003</v>
       </c>
       <c r="F46" s="2">
-        <v>0.31</v>
+        <v>1.06</v>
       </c>
       <c r="G46" s="3">
-        <f t="shared" si="3"/>
-        <v>0.09</v>
+        <f>ROUND(STDEV(I46:M46)/SQRT(COUNT(I46:M46)),2)</f>
+        <v>1.04</v>
       </c>
       <c r="H46" s="2">
         <v>5</v>
       </c>
       <c r="I46" s="4">
-        <v>3.84</v>
+        <v>2.63</v>
       </c>
       <c r="J46" s="2">
-        <v>4.01</v>
+        <v>4.24</v>
       </c>
       <c r="K46" s="2">
-        <v>4.2699999999999996</v>
+        <v>5.54</v>
       </c>
       <c r="L46" s="2">
-        <v>4.29</v>
+        <v>7.03</v>
       </c>
       <c r="M46" s="2">
-        <v>3.89</v>
+        <v>1.1100000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B47" t="s">
         <v>28</v>
       </c>
       <c r="C47" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D47" s="2">
-        <v>5.67</v>
+        <v>4.13</v>
       </c>
       <c r="E47" s="3">
-        <f t="shared" si="2"/>
-        <v>5.3179999999999996</v>
+        <f>AVERAGE(I47:M47)</f>
+        <v>2.4739999999999998</v>
       </c>
       <c r="F47" s="2">
-        <v>0.5</v>
+        <v>1.05</v>
       </c>
       <c r="G47" s="3">
-        <f t="shared" si="3"/>
-        <v>0.26</v>
+        <f>ROUND(STDEV(I47:M47)/SQRT(COUNT(I47:M47)),2)</f>
+        <v>0.6</v>
       </c>
       <c r="H47" s="2">
         <v>5</v>
       </c>
       <c r="I47" s="4">
-        <v>6.27</v>
+        <v>2.11</v>
       </c>
       <c r="J47" s="2">
-        <v>4.95</v>
+        <v>1.83</v>
       </c>
       <c r="K47" s="2">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="L47" s="2">
-        <v>5.17</v>
+        <v>1.22</v>
       </c>
       <c r="M47" s="2">
-        <v>4.8</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>16</v>
-      </c>
-      <c r="B48" t="s">
-        <v>28</v>
-      </c>
-      <c r="C48" t="s">
-        <v>7</v>
+      <c r="A48" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="D48" s="2">
-        <v>1.34</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="E48" s="3">
-        <f t="shared" si="2"/>
-        <v>1.238</v>
+        <f>AVERAGE(I48:M48)</f>
+        <v>2.5840000000000001</v>
       </c>
       <c r="F48" s="2">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="G48" s="3">
-        <f t="shared" si="3"/>
-        <v>0.17</v>
+        <f>ROUND(STDEV(I48:M48)/SQRT(COUNT(I48:M48)),2)</f>
+        <v>0.16</v>
       </c>
       <c r="H48" s="2">
         <v>5</v>
       </c>
       <c r="I48" s="4">
-        <v>1.05</v>
+        <v>2.64</v>
       </c>
       <c r="J48" s="2">
-        <v>0.83</v>
+        <v>2.97</v>
       </c>
       <c r="K48" s="2">
-        <v>1.81</v>
+        <v>2.37</v>
       </c>
       <c r="L48" s="2">
-        <v>1.39</v>
+        <v>2.1</v>
       </c>
       <c r="M48" s="2">
-        <v>1.1100000000000001</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C49" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D49" s="2">
-        <v>1.57</v>
+        <v>2.68</v>
       </c>
       <c r="E49" s="3">
-        <f t="shared" si="2"/>
-        <v>1.488</v>
+        <f>AVERAGE(I49:M49)</f>
+        <v>3.0940000000000003</v>
       </c>
       <c r="F49" s="2">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="G49" s="3">
-        <f t="shared" si="3"/>
-        <v>0.22</v>
+        <f>ROUND(STDEV(I49:M49)/SQRT(COUNT(I49:M49)),2)</f>
+        <v>0.24</v>
       </c>
       <c r="H49" s="2">
         <v>5</v>
       </c>
       <c r="I49" s="4">
-        <v>2.1800000000000002</v>
+        <v>2.67</v>
       </c>
       <c r="J49" s="2">
-        <v>1.56</v>
+        <v>3.07</v>
       </c>
       <c r="K49" s="2">
-        <v>0.8</v>
+        <v>2.74</v>
       </c>
       <c r="L49" s="2">
-        <v>1.43</v>
+        <v>2.97</v>
       </c>
       <c r="M49" s="2">
-        <v>1.47</v>
+        <v>4.0199999999999996</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>16</v>
-      </c>
-      <c r="B50" t="s">
-        <v>28</v>
-      </c>
-      <c r="C50" t="s">
-        <v>10</v>
+      <c r="A50" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="D50" s="2">
-        <v>4.13</v>
+        <v>1.41</v>
       </c>
       <c r="E50" s="3">
-        <f t="shared" si="2"/>
-        <v>2.4739999999999998</v>
+        <f>AVERAGE(I50:M50)</f>
+        <v>1.516</v>
       </c>
       <c r="F50" s="2">
-        <v>1.05</v>
+        <v>0.13</v>
       </c>
       <c r="G50" s="3">
-        <f t="shared" si="3"/>
-        <v>0.6</v>
+        <f>ROUND(STDEV(I50:M50)/SQRT(COUNT(I50:M50)),2)</f>
+        <v>0.12</v>
       </c>
       <c r="H50" s="2">
         <v>5</v>
       </c>
       <c r="I50" s="4">
-        <v>2.11</v>
+        <v>1.58</v>
       </c>
       <c r="J50" s="2">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="K50" s="2">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="L50" s="2">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="M50" s="2">
-        <v>4.71</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
@@ -3087,85 +3090,85 @@
         <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D51" s="2">
-        <v>1.77</v>
+        <v>1.32</v>
       </c>
       <c r="E51" s="3">
-        <f t="shared" si="2"/>
-        <v>1.6280000000000001</v>
+        <f>AVERAGE(I51:M51)</f>
+        <v>1.532</v>
       </c>
       <c r="F51" s="2">
-        <v>0.28000000000000003</v>
+        <v>0.19</v>
       </c>
       <c r="G51" s="3">
-        <f t="shared" si="3"/>
-        <v>0.39</v>
+        <f>ROUND(STDEV(I51:M51)/SQRT(COUNT(I51:M51)),2)</f>
+        <v>0.19</v>
       </c>
       <c r="H51" s="2">
         <v>5</v>
       </c>
       <c r="I51" s="4">
+        <v>2.19</v>
+      </c>
+      <c r="J51" s="2">
+        <v>1.36</v>
+      </c>
+      <c r="K51" s="2">
+        <v>1.02</v>
+      </c>
+      <c r="L51" s="2">
+        <v>1.64</v>
+      </c>
+      <c r="M51" s="2">
         <v>1.45</v>
-      </c>
-      <c r="J51" s="2">
-        <v>2.7</v>
-      </c>
-      <c r="K51" s="2">
-        <v>0.94</v>
-      </c>
-      <c r="L51" s="2">
-        <v>0.72</v>
-      </c>
-      <c r="M51" s="2">
-        <v>2.33</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C52" t="s">
         <v>5</v>
       </c>
       <c r="D52" s="2">
-        <v>4.32</v>
+        <v>1.34</v>
       </c>
       <c r="E52" s="3">
-        <f t="shared" si="2"/>
-        <v>4.4820000000000002</v>
+        <f>AVERAGE(I52:M52)</f>
+        <v>1.5680000000000001</v>
       </c>
       <c r="F52" s="2">
-        <v>0.54</v>
+        <v>0.31</v>
       </c>
       <c r="G52" s="3">
-        <f t="shared" si="3"/>
-        <v>0.6</v>
+        <f>ROUND(STDEV(I52:M52)/SQRT(COUNT(I52:M52)),2)</f>
+        <v>0.22</v>
       </c>
       <c r="H52" s="2">
         <v>5</v>
       </c>
       <c r="I52" s="4">
-        <v>6.84</v>
+        <v>1.22</v>
       </c>
       <c r="J52" s="2">
-        <v>3.65</v>
+        <v>2.02</v>
       </c>
       <c r="K52" s="2">
-        <v>3.62</v>
+        <v>2.16</v>
       </c>
       <c r="L52" s="2">
-        <v>4.07</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="M52" s="2">
-        <v>4.2300000000000004</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.2">
@@ -3182,14 +3185,14 @@
         <v>1.44</v>
       </c>
       <c r="E53" s="3">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(I53:M53)</f>
         <v>1.3080000000000001</v>
       </c>
       <c r="F53" s="2">
         <v>0.27</v>
       </c>
       <c r="G53" s="3">
-        <f t="shared" si="3"/>
+        <f>ROUND(STDEV(I53:M53)/SQRT(COUNT(I53:M53)),2)</f>
         <v>0.36</v>
       </c>
       <c r="H53" s="2">
@@ -3212,46 +3215,46 @@
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>16</v>
-      </c>
-      <c r="B54" t="s">
-        <v>28</v>
-      </c>
-      <c r="C54" t="s">
-        <v>8</v>
+      <c r="A54" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="D54" s="2">
-        <v>0.19</v>
+        <v>1.34</v>
       </c>
       <c r="E54" s="3">
-        <f t="shared" si="2"/>
-        <v>0.188</v>
+        <f>AVERAGE(I54:M54)</f>
+        <v>1.286</v>
       </c>
       <c r="F54" s="2">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G54" s="3">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
+        <f>ROUND(STDEV(I54:M54)/SQRT(COUNT(I54:M54)),2)</f>
+        <v>0.06</v>
       </c>
       <c r="H54" s="2">
         <v>5</v>
       </c>
       <c r="I54" s="4">
-        <v>0.19</v>
+        <v>1.29</v>
       </c>
       <c r="J54" s="2">
-        <v>0.16</v>
+        <v>1.4</v>
       </c>
       <c r="K54" s="2">
-        <v>0.21</v>
+        <v>1.23</v>
       </c>
       <c r="L54" s="2">
-        <v>0.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="M54" s="2">
-        <v>0.18</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
@@ -3259,214 +3262,214 @@
         <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C55" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D55" s="2">
-        <v>1.1200000000000001</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="E55" s="3">
-        <f t="shared" si="2"/>
-        <v>1.0840000000000001</v>
+        <f>AVERAGE(I55:M55)</f>
+        <v>0.83799999999999986</v>
       </c>
       <c r="F55" s="2">
-        <v>0.04</v>
+        <v>0.13</v>
       </c>
       <c r="G55" s="3">
-        <f t="shared" si="3"/>
-        <v>0.03</v>
+        <f>ROUND(STDEV(I55:M55)/SQRT(COUNT(I55:M55)),2)</f>
+        <v>0.11</v>
       </c>
       <c r="H55" s="2">
         <v>5</v>
       </c>
       <c r="I55" s="4">
-        <v>1.08</v>
+        <v>0.79</v>
       </c>
       <c r="J55" s="2">
-        <v>1.1599999999999999</v>
+        <v>1.24</v>
       </c>
       <c r="K55" s="2">
-        <v>1.1499999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="L55" s="2">
-        <v>1.02</v>
+        <v>0.8</v>
       </c>
       <c r="M55" s="2">
-        <v>1.01</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>16</v>
-      </c>
-      <c r="B56" t="s">
-        <v>28</v>
-      </c>
-      <c r="C56" t="s">
-        <v>6</v>
+      <c r="A56" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="D56" s="2">
-        <v>5.1100000000000003</v>
+        <v>3.14</v>
       </c>
       <c r="E56" s="3">
-        <f t="shared" si="2"/>
-        <v>5.42</v>
+        <f>AVERAGE(I56:M56)</f>
+        <v>3.048</v>
       </c>
       <c r="F56" s="2">
-        <v>0.72</v>
+        <v>0.31</v>
       </c>
       <c r="G56" s="3">
-        <f t="shared" si="3"/>
-        <v>0.97</v>
+        <f>ROUND(STDEV(I56:M56)/SQRT(COUNT(I56:M56)),2)</f>
+        <v>0.42</v>
       </c>
       <c r="H56" s="2">
         <v>5</v>
       </c>
       <c r="I56" s="4">
-        <v>4.37</v>
+        <v>3.87</v>
       </c>
       <c r="J56" s="2">
-        <v>7.03</v>
+        <v>3.77</v>
       </c>
       <c r="K56" s="2">
-        <v>6</v>
+        <v>1.64</v>
       </c>
       <c r="L56" s="2">
-        <v>7.5</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="M56" s="2">
-        <v>2.2000000000000002</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B57" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" s="2">
+        <v>2.77</v>
+      </c>
+      <c r="E57" s="3">
+        <f>AVERAGE(I57:M57)</f>
+        <v>4.016</v>
+      </c>
+      <c r="F57" s="2">
+        <v>0.74</v>
+      </c>
+      <c r="G57" s="3">
+        <f>ROUND(STDEV(I57:M57)/SQRT(COUNT(I57:M57)),2)</f>
+        <v>0.47</v>
+      </c>
+      <c r="H57" s="2">
+        <v>5</v>
+      </c>
+      <c r="I57" s="4">
+        <v>5.2</v>
+      </c>
+      <c r="J57" s="2">
+        <v>2.78</v>
+      </c>
+      <c r="K57" s="2">
+        <v>3.87</v>
+      </c>
+      <c r="L57" s="2">
+        <v>3.29</v>
+      </c>
+      <c r="M57" s="2">
+        <v>4.9400000000000004</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>16</v>
+      </c>
+      <c r="B58" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" s="2">
+        <v>3.15</v>
+      </c>
+      <c r="E58" s="3">
+        <f>AVERAGE(I58:M58)</f>
+        <v>2.9180000000000001</v>
+      </c>
+      <c r="F58" s="2">
+        <v>0.43</v>
+      </c>
+      <c r="G58" s="3">
+        <f>ROUND(STDEV(I58:M58)/SQRT(COUNT(I58:M58)),2)</f>
+        <v>0.54</v>
+      </c>
+      <c r="H58" s="2">
+        <v>5</v>
+      </c>
+      <c r="I58" s="4">
+        <v>2.66</v>
+      </c>
+      <c r="J58" s="2">
+        <v>3.98</v>
+      </c>
+      <c r="K58" s="2">
+        <v>4.38</v>
+      </c>
+      <c r="L58" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="M58" s="2">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>16</v>
+      </c>
+      <c r="B59" t="s">
         <v>28</v>
       </c>
-      <c r="C57" t="s">
-        <v>6</v>
-      </c>
-      <c r="D57" s="2">
-        <v>2.88</v>
-      </c>
-      <c r="E57" s="3">
-        <f t="shared" si="2"/>
-        <v>2.726</v>
-      </c>
-      <c r="F57" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="G57" s="3">
-        <f t="shared" si="3"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="H57" s="2">
-        <v>5</v>
-      </c>
-      <c r="I57" s="4">
-        <v>2.56</v>
-      </c>
-      <c r="J57" s="2">
-        <v>2.81</v>
-      </c>
-      <c r="K57" s="2">
-        <v>2.69</v>
-      </c>
-      <c r="L57" s="2">
-        <v>2.97</v>
-      </c>
-      <c r="M57" s="2">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A58" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D58" s="2">
-        <v>0.33</v>
-      </c>
-      <c r="E58" s="3">
-        <f t="shared" si="2"/>
-        <v>0.65000000000000013</v>
-      </c>
-      <c r="F58" s="2">
-        <v>0.59</v>
-      </c>
-      <c r="G58" s="3">
-        <f t="shared" si="3"/>
-        <v>0.15</v>
-      </c>
-      <c r="H58" s="2">
-        <v>5</v>
-      </c>
-      <c r="I58" s="4">
-        <v>1.17</v>
-      </c>
-      <c r="J58" s="2">
-        <v>0.39</v>
-      </c>
-      <c r="K58" s="2">
-        <v>0.83</v>
-      </c>
-      <c r="L58" s="2">
-        <v>0.45</v>
-      </c>
-      <c r="M58" s="2">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A59" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>11</v>
+      <c r="C59" t="s">
+        <v>5</v>
       </c>
       <c r="D59" s="2">
-        <v>0.28999999999999998</v>
+        <v>4.32</v>
       </c>
       <c r="E59" s="3">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <f>AVERAGE(I59:M59)</f>
+        <v>4.4820000000000002</v>
       </c>
       <c r="F59" s="2">
-        <v>0.13</v>
+        <v>0.54</v>
       </c>
       <c r="G59" s="3">
-        <f t="shared" si="3"/>
-        <v>0.08</v>
+        <f>ROUND(STDEV(I59:M59)/SQRT(COUNT(I59:M59)),2)</f>
+        <v>0.6</v>
       </c>
       <c r="H59" s="2">
         <v>5</v>
       </c>
       <c r="I59" s="4">
-        <v>0.51</v>
+        <v>6.84</v>
       </c>
       <c r="J59" s="2">
-        <v>0.09</v>
+        <v>3.65</v>
       </c>
       <c r="K59" s="2">
-        <v>0.28000000000000003</v>
+        <v>3.62</v>
       </c>
       <c r="L59" s="2">
-        <v>0.34</v>
+        <v>4.07</v>
       </c>
       <c r="M59" s="2">
-        <v>0.06</v>
+        <v>4.2300000000000004</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
@@ -3477,340 +3480,340 @@
         <v>30</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D60" s="2">
-        <v>6.15</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="E60" s="3">
-        <f t="shared" si="2"/>
-        <v>5.9320000000000004</v>
+        <f>AVERAGE(I60:M60)</f>
+        <v>2.056</v>
       </c>
       <c r="F60" s="2">
-        <v>0.48</v>
+        <v>0.09</v>
       </c>
       <c r="G60" s="3">
-        <f t="shared" si="3"/>
-        <v>0.19</v>
+        <f>ROUND(STDEV(I60:M60)/SQRT(COUNT(I60:M60)),2)</f>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H60" s="2">
         <v>5</v>
       </c>
       <c r="I60" s="4">
-        <v>6.28</v>
+        <v>1.94</v>
       </c>
       <c r="J60" s="2">
-        <v>6.29</v>
+        <v>1.96</v>
       </c>
       <c r="K60" s="2">
-        <v>5.23</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="L60" s="2">
-        <v>5.96</v>
+        <v>1.91</v>
       </c>
       <c r="M60" s="2">
-        <v>5.9</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A61" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>9</v>
+      <c r="A61" t="s">
+        <v>16</v>
+      </c>
+      <c r="B61" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61" t="s">
+        <v>5</v>
       </c>
       <c r="D61" s="2">
-        <v>5.19</v>
+        <v>1.32</v>
       </c>
       <c r="E61" s="3">
-        <f t="shared" si="2"/>
-        <v>4.9539999999999988</v>
+        <f>AVERAGE(I61:M61)</f>
+        <v>1.1559999999999999</v>
       </c>
       <c r="F61" s="2">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="G61" s="3">
-        <f t="shared" si="3"/>
-        <v>0.48</v>
+        <f>ROUND(STDEV(I61:M61)/SQRT(COUNT(I61:M61)),2)</f>
+        <v>0.15</v>
       </c>
       <c r="H61" s="2">
         <v>5</v>
       </c>
       <c r="I61" s="4">
-        <v>5.33</v>
+        <v>1.39</v>
       </c>
       <c r="J61" s="2">
-        <v>5.23</v>
+        <v>0.86</v>
       </c>
       <c r="K61" s="2">
-        <v>5.98</v>
+        <v>1.54</v>
       </c>
       <c r="L61" s="2">
-        <v>3.15</v>
+        <v>1.23</v>
       </c>
       <c r="M61" s="2">
-        <v>5.08</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D62" s="2">
-        <v>1.95</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E62" s="3">
-        <f t="shared" si="2"/>
-        <v>1.6719999999999999</v>
+        <f>AVERAGE(I62:M62)</f>
+        <v>0.53400000000000003</v>
       </c>
       <c r="F62" s="2">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="G62" s="3">
-        <f t="shared" si="3"/>
-        <v>0.19</v>
+        <f>ROUND(STDEV(I62:M62)/SQRT(COUNT(I62:M62)),2)</f>
+        <v>0.03</v>
       </c>
       <c r="H62" s="2">
         <v>5</v>
       </c>
       <c r="I62" s="4">
-        <v>0.92</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="J62" s="2">
-        <v>2</v>
+        <v>0.47</v>
       </c>
       <c r="K62" s="2">
-        <v>1.69</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L62" s="2">
-        <v>1.84</v>
+        <v>0.48</v>
       </c>
       <c r="M62" s="2">
-        <v>1.91</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A63" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>7</v>
+      <c r="A63" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" t="s">
+        <v>8</v>
       </c>
       <c r="D63" s="2">
-        <v>0.59</v>
+        <v>0.42</v>
       </c>
       <c r="E63" s="3">
-        <f t="shared" si="2"/>
-        <v>0.45199999999999996</v>
+        <f>AVERAGE(I63:M63)</f>
+        <v>0.7340000000000001</v>
       </c>
       <c r="F63" s="2">
         <v>0.24</v>
       </c>
       <c r="G63" s="3">
-        <f t="shared" si="3"/>
-        <v>0.25</v>
+        <f>ROUND(STDEV(I63:M63)/SQRT(COUNT(I63:M63)),2)</f>
+        <v>0.17</v>
       </c>
       <c r="H63" s="2">
         <v>5</v>
       </c>
       <c r="I63" s="4">
-        <v>0.28999999999999998</v>
+        <v>1</v>
       </c>
       <c r="J63" s="2">
-        <v>1.41</v>
+        <v>0.8</v>
       </c>
       <c r="K63" s="2">
         <v>0.11</v>
       </c>
       <c r="L63" s="2">
-        <v>0.42</v>
+        <v>0.7</v>
       </c>
       <c r="M63" s="2">
-        <v>0.03</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A64" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>10</v>
+      <c r="A64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" t="s">
+        <v>27</v>
+      </c>
+      <c r="C64" t="s">
+        <v>8</v>
       </c>
       <c r="D64" s="2">
-        <v>2.5499999999999998</v>
+        <v>0.75</v>
       </c>
       <c r="E64" s="3">
-        <f t="shared" si="2"/>
-        <v>2.5840000000000001</v>
+        <f>AVERAGE(I64:M64)</f>
+        <v>0.81199999999999994</v>
       </c>
       <c r="F64" s="2">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="G64" s="3">
-        <f t="shared" si="3"/>
-        <v>0.16</v>
+        <f>ROUND(STDEV(I64:M64)/SQRT(COUNT(I64:M64)),2)</f>
+        <v>0.12</v>
       </c>
       <c r="H64" s="2">
         <v>5</v>
       </c>
       <c r="I64" s="4">
-        <v>2.64</v>
+        <v>0.97</v>
       </c>
       <c r="J64" s="2">
-        <v>2.97</v>
+        <v>0.5</v>
       </c>
       <c r="K64" s="2">
-        <v>2.37</v>
+        <v>0.66</v>
       </c>
       <c r="L64" s="2">
-        <v>2.1</v>
+        <v>1.17</v>
       </c>
       <c r="M64" s="2">
-        <v>2.84</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A65" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>10</v>
+      <c r="A65" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65" t="s">
+        <v>8</v>
       </c>
       <c r="D65" s="2">
         <v>1.1200000000000001</v>
       </c>
       <c r="E65" s="3">
-        <f t="shared" si="2"/>
-        <v>1.1919999999999999</v>
+        <f>AVERAGE(I65:M65)</f>
+        <v>1.0840000000000001</v>
       </c>
       <c r="F65" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.04</v>
       </c>
       <c r="G65" s="3">
-        <f t="shared" si="3"/>
-        <v>0.05</v>
+        <f>ROUND(STDEV(I65:M65)/SQRT(COUNT(I65:M65)),2)</f>
+        <v>0.03</v>
       </c>
       <c r="H65" s="2">
         <v>5</v>
       </c>
       <c r="I65" s="4">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="J65" s="2">
-        <v>1.18</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="K65" s="2">
-        <v>1.25</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="L65" s="2">
-        <v>1.1399999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="M65" s="2">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D66" s="2">
-        <v>2.0099999999999998</v>
+        <v>0.26</v>
       </c>
       <c r="E66" s="3">
-        <f t="shared" ref="E66:E85" si="4">AVERAGE(I66:M66)</f>
-        <v>2.056</v>
+        <f>AVERAGE(I66:M66)</f>
+        <v>0.28800000000000003</v>
       </c>
       <c r="F66" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="G66" s="3">
+        <f>ROUND(STDEV(I66:M66)/SQRT(COUNT(I66:M66)),2)</f>
+        <v>0.01</v>
+      </c>
+      <c r="H66" s="2">
+        <v>5</v>
+      </c>
+      <c r="I66" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="J66" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="K66" s="2">
+        <v>0.33</v>
+      </c>
+      <c r="L66" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="M66" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67" t="s">
+        <v>25</v>
+      </c>
+      <c r="C67" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2">
+        <v>0.33</v>
+      </c>
+      <c r="E67" s="3">
+        <f>AVERAGE(I67:M67)</f>
+        <v>0.378</v>
+      </c>
+      <c r="F67" s="2">
         <v>0.09</v>
       </c>
-      <c r="G66" s="3">
-        <f t="shared" ref="G66:G85" si="5">ROUND(STDEV(I66:M66)/SQRT(COUNT(I66:M66)),2)</f>
+      <c r="G67" s="3">
+        <f>ROUND(STDEV(I67:M67)/SQRT(COUNT(I67:M67)),2)</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H66" s="2">
-        <v>5</v>
-      </c>
-      <c r="I66" s="4">
-        <v>1.94</v>
-      </c>
-      <c r="J66" s="2">
-        <v>1.96</v>
-      </c>
-      <c r="K66" s="2">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="L66" s="2">
-        <v>1.91</v>
-      </c>
-      <c r="M66" s="2">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A67" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D67" s="2">
-        <v>1.34</v>
-      </c>
-      <c r="E67" s="3">
-        <f t="shared" si="4"/>
-        <v>1.286</v>
-      </c>
-      <c r="F67" s="2">
-        <v>0.04</v>
-      </c>
-      <c r="G67" s="3">
-        <f t="shared" si="5"/>
-        <v>0.06</v>
-      </c>
       <c r="H67" s="2">
         <v>5</v>
       </c>
       <c r="I67" s="4">
-        <v>1.29</v>
+        <v>0.22</v>
       </c>
       <c r="J67" s="2">
-        <v>1.4</v>
+        <v>0.32</v>
       </c>
       <c r="K67" s="2">
-        <v>1.23</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="L67" s="2">
-        <v>1.1000000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="M67" s="2">
-        <v>1.41</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.2">
@@ -3818,67 +3821,67 @@
         <v>16</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="2">
-        <v>0.39</v>
+        <v>0.31</v>
       </c>
       <c r="E68" s="3">
-        <f t="shared" si="4"/>
-        <v>0.4</v>
+        <f>AVERAGE(I68:M68)</f>
+        <v>0.30199999999999999</v>
       </c>
       <c r="F68" s="2">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G68" s="3">
-        <f t="shared" si="5"/>
+        <f>ROUND(STDEV(I68:M68)/SQRT(COUNT(I68:M68)),2)</f>
         <v>0.01</v>
       </c>
       <c r="H68" s="2">
         <v>5</v>
       </c>
       <c r="I68" s="4">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J68" s="2">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="K68" s="2">
-        <v>0.41</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="L68" s="2">
-        <v>0.41</v>
+        <v>0.33</v>
       </c>
       <c r="M68" s="2">
-        <v>0.36</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A69" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C69" s="6" t="s">
+      <c r="A69" t="s">
+        <v>16</v>
+      </c>
+      <c r="B69" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="2">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="E69" s="3">
-        <f t="shared" si="4"/>
-        <v>0.28800000000000003</v>
+        <f>AVERAGE(I69:M69)</f>
+        <v>0.246</v>
       </c>
       <c r="F69" s="2">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="G69" s="3">
-        <f t="shared" si="5"/>
-        <v>0.01</v>
+        <f>ROUND(STDEV(I69:M69)/SQRT(COUNT(I69:M69)),2)</f>
+        <v>0.08</v>
       </c>
       <c r="H69" s="2">
         <v>5</v>
@@ -3887,231 +3890,231 @@
         <v>0.25</v>
       </c>
       <c r="J69" s="2">
-        <v>0.27</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="K69" s="2">
-        <v>0.33</v>
+        <v>0.19</v>
       </c>
       <c r="L69" s="2">
-        <v>0.28999999999999998</v>
+        <v>0.09</v>
       </c>
       <c r="M69" s="2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>16</v>
+      </c>
+      <c r="B70" t="s">
+        <v>27</v>
+      </c>
+      <c r="C70" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2">
+        <v>0.24</v>
+      </c>
+      <c r="E70" s="3">
+        <f>AVERAGE(I70:M70)</f>
+        <v>0.23199999999999998</v>
+      </c>
+      <c r="F70" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="G70" s="3">
+        <f>ROUND(STDEV(I70:M70)/SQRT(COUNT(I70:M70)),2)</f>
+        <v>0.04</v>
+      </c>
+      <c r="H70" s="2">
+        <v>5</v>
+      </c>
+      <c r="I70" s="4">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A70" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B70" s="6" t="s">
+      <c r="J70" s="2">
+        <v>0.34</v>
+      </c>
+      <c r="K70" s="2">
+        <v>0.24</v>
+      </c>
+      <c r="L70" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="M70" s="2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>16</v>
+      </c>
+      <c r="B71" t="s">
+        <v>28</v>
+      </c>
+      <c r="C71" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="2">
+        <v>0.19</v>
+      </c>
+      <c r="E71" s="3">
+        <f>AVERAGE(I71:M71)</f>
+        <v>0.188</v>
+      </c>
+      <c r="F71" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="G71" s="3">
+        <f>ROUND(STDEV(I71:M71)/SQRT(COUNT(I71:M71)),2)</f>
+        <v>0.01</v>
+      </c>
+      <c r="H71" s="2">
+        <v>5</v>
+      </c>
+      <c r="I71" s="4">
+        <v>0.19</v>
+      </c>
+      <c r="J71" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="K71" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="L71" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="M71" s="2">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A72" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B72" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C70" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D70" s="2">
-        <v>4.1100000000000003</v>
-      </c>
-      <c r="E70" s="3">
-        <f t="shared" si="4"/>
-        <v>3.9480000000000004</v>
-      </c>
-      <c r="F70" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="G70" s="3">
-        <f t="shared" si="5"/>
-        <v>0.11</v>
-      </c>
-      <c r="H70" s="2">
-        <v>5</v>
-      </c>
-      <c r="I70" s="4">
-        <v>4.01</v>
-      </c>
-      <c r="J70" s="2">
-        <v>3.67</v>
-      </c>
-      <c r="K70" s="2">
-        <v>3.71</v>
-      </c>
-      <c r="L70" s="2">
-        <v>4.08</v>
-      </c>
-      <c r="M70" s="2">
-        <v>4.2699999999999996</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A71" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D71" s="2">
-        <v>2.77</v>
-      </c>
-      <c r="E71" s="3">
-        <f t="shared" si="4"/>
-        <v>2.6160000000000001</v>
-      </c>
-      <c r="F71" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="G71" s="3">
-        <f t="shared" si="5"/>
-        <v>0.21</v>
-      </c>
-      <c r="H71" s="2">
-        <v>5</v>
-      </c>
-      <c r="I71" s="4">
-        <v>3.29</v>
-      </c>
-      <c r="J71" s="2">
-        <v>2.75</v>
-      </c>
-      <c r="K71" s="2">
-        <v>2.66</v>
-      </c>
-      <c r="L71" s="2">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="M71" s="2">
-        <v>2.31</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>16</v>
-      </c>
-      <c r="B72" t="s">
-        <v>25</v>
-      </c>
-      <c r="C72" t="s">
-        <v>11</v>
+      <c r="C72" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="D72" s="2">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="E72" s="3">
-        <f t="shared" si="4"/>
-        <v>0.23199999999999998</v>
+        <f>AVERAGE(I72:M72)</f>
+        <v>0.4</v>
       </c>
       <c r="F72" s="2">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G72" s="3">
-        <f t="shared" si="5"/>
-        <v>0.03</v>
+        <f>ROUND(STDEV(I72:M72)/SQRT(COUNT(I72:M72)),2)</f>
+        <v>0.01</v>
       </c>
       <c r="H72" s="2">
         <v>5</v>
       </c>
       <c r="I72" s="4">
-        <v>0.13</v>
+        <v>0.4</v>
       </c>
       <c r="J72" s="2">
-        <v>0.23</v>
+        <v>0.42</v>
       </c>
       <c r="K72" s="2">
-        <v>0.25</v>
+        <v>0.41</v>
       </c>
       <c r="L72" s="2">
-        <v>0.34</v>
+        <v>0.41</v>
       </c>
       <c r="M72" s="2">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B73" t="s">
         <v>25</v>
       </c>
       <c r="C73" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D73" s="2">
-        <v>0.21</v>
+        <v>0.45</v>
       </c>
       <c r="E73" s="3">
-        <f t="shared" si="4"/>
-        <v>0.27600000000000002</v>
+        <f>AVERAGE(I73:M73)</f>
+        <v>0.49199999999999999</v>
       </c>
       <c r="F73" s="2">
-        <v>0.12</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G73" s="3">
-        <f t="shared" si="5"/>
+        <f>ROUND(STDEV(I73:M73)/SQRT(COUNT(I73:M73)),2)</f>
+        <v>0.11</v>
+      </c>
+      <c r="H73" s="2">
+        <v>5</v>
+      </c>
+      <c r="I73" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="J73" s="2">
+        <v>0.49</v>
+      </c>
+      <c r="K73" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="L73" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="M73" s="2">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A74" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D74" s="2">
+        <v>2.19</v>
+      </c>
+      <c r="E74" s="3">
+        <f>AVERAGE(I74:M74)</f>
+        <v>2.218</v>
+      </c>
+      <c r="F74" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="G74" s="3">
+        <f>ROUND(STDEV(I74:M74)/SQRT(COUNT(I74:M74)),2)</f>
         <v>0.05</v>
       </c>
-      <c r="H73" s="2">
-        <v>4</v>
-      </c>
-      <c r="I73" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="J73" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="K73" s="2">
-        <v>0.42</v>
-      </c>
-      <c r="L73" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="M73" s="2">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>16</v>
-      </c>
-      <c r="B74" t="s">
-        <v>25</v>
-      </c>
-      <c r="C74" t="s">
-        <v>9</v>
-      </c>
-      <c r="D74" s="2">
-        <v>7.2</v>
-      </c>
-      <c r="E74" s="3">
-        <f t="shared" si="4"/>
-        <v>7.1059999999999999</v>
-      </c>
-      <c r="F74" s="2">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="G74" s="3">
-        <f t="shared" si="5"/>
-        <v>1.63</v>
-      </c>
       <c r="H74" s="2">
         <v>5</v>
       </c>
       <c r="I74" s="4">
-        <v>4.0999999999999996</v>
+        <v>2.29</v>
       </c>
       <c r="J74" s="2">
-        <v>8.4499999999999993</v>
+        <v>2.23</v>
       </c>
       <c r="K74" s="2">
-        <v>9.6</v>
+        <v>2.34</v>
       </c>
       <c r="L74" s="2">
-        <v>2.4500000000000002</v>
+        <v>2.15</v>
       </c>
       <c r="M74" s="2">
-        <v>10.93</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.2">
@@ -4119,85 +4122,85 @@
         <v>3</v>
       </c>
       <c r="B75" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C75" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D75" s="2">
-        <v>4.4400000000000004</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="E75" s="3">
-        <f t="shared" si="4"/>
-        <v>4.3339999999999996</v>
+        <f>AVERAGE(I75:M75)</f>
+        <v>2.1259999999999999</v>
       </c>
       <c r="F75" s="2">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="G75" s="3">
-        <f t="shared" si="5"/>
-        <v>0.08</v>
+        <f>ROUND(STDEV(I75:M75)/SQRT(COUNT(I75:M75)),2)</f>
+        <v>0.28000000000000003</v>
       </c>
       <c r="H75" s="2">
         <v>5</v>
       </c>
       <c r="I75" s="4">
-        <v>4.58</v>
+        <v>2.73</v>
       </c>
       <c r="J75" s="2">
-        <v>4.17</v>
+        <v>1.7</v>
       </c>
       <c r="K75" s="2">
-        <v>4.41</v>
+        <v>2.52</v>
       </c>
       <c r="L75" s="2">
-        <v>4.3499999999999996</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="M75" s="2">
-        <v>4.16</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B76" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C76" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D76" s="2">
-        <v>1.77</v>
+        <v>3.1</v>
       </c>
       <c r="E76" s="3">
-        <f t="shared" si="4"/>
-        <v>1.6440000000000001</v>
+        <f>AVERAGE(I76:M76)</f>
+        <v>3.5020000000000002</v>
       </c>
       <c r="F76" s="2">
-        <v>0.13</v>
+        <v>0.54</v>
       </c>
       <c r="G76" s="3">
-        <f t="shared" si="5"/>
-        <v>0.17</v>
+        <f>ROUND(STDEV(I76:M76)/SQRT(COUNT(I76:M76)),2)</f>
+        <v>0.66</v>
       </c>
       <c r="H76" s="2">
         <v>5</v>
       </c>
       <c r="I76" s="4">
-        <v>2.21</v>
+        <v>3.77</v>
       </c>
       <c r="J76" s="2">
-        <v>1.36</v>
+        <v>1.76</v>
       </c>
       <c r="K76" s="2">
-        <v>1.64</v>
+        <v>2.36</v>
       </c>
       <c r="L76" s="2">
-        <v>1.79</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="M76" s="2">
-        <v>1.22</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.2">
@@ -4205,85 +4208,85 @@
         <v>3</v>
       </c>
       <c r="B77" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C77" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D77" s="2">
-        <v>0.64</v>
+        <v>2.88</v>
       </c>
       <c r="E77" s="3">
-        <f t="shared" si="4"/>
-        <v>0.78999999999999992</v>
+        <f>AVERAGE(I77:M77)</f>
+        <v>2.726</v>
       </c>
       <c r="F77" s="2">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="G77" s="3">
-        <f t="shared" si="5"/>
-        <v>0.09</v>
+        <f>ROUND(STDEV(I77:M77)/SQRT(COUNT(I77:M77)),2)</f>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H77" s="2">
         <v>5</v>
       </c>
       <c r="I77" s="4">
-        <v>0.94</v>
+        <v>2.56</v>
       </c>
       <c r="J77" s="2">
-        <v>1.04</v>
+        <v>2.81</v>
       </c>
       <c r="K77" s="2">
-        <v>0.73</v>
+        <v>2.69</v>
       </c>
       <c r="L77" s="2">
-        <v>0.59</v>
+        <v>2.97</v>
       </c>
       <c r="M77" s="2">
-        <v>0.65</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>16</v>
-      </c>
-      <c r="B78" t="s">
-        <v>25</v>
-      </c>
-      <c r="C78" t="s">
-        <v>10</v>
+      <c r="A78" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="D78" s="2">
-        <v>2.68</v>
+        <v>2.77</v>
       </c>
       <c r="E78" s="3">
-        <f t="shared" si="4"/>
-        <v>3.0940000000000003</v>
+        <f>AVERAGE(I78:M78)</f>
+        <v>2.6160000000000001</v>
       </c>
       <c r="F78" s="2">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G78" s="3">
-        <f t="shared" si="5"/>
-        <v>0.24</v>
+        <f>ROUND(STDEV(I78:M78)/SQRT(COUNT(I78:M78)),2)</f>
+        <v>0.21</v>
       </c>
       <c r="H78" s="2">
         <v>5</v>
       </c>
       <c r="I78" s="4">
-        <v>2.67</v>
+        <v>3.29</v>
       </c>
       <c r="J78" s="2">
-        <v>3.07</v>
+        <v>2.75</v>
       </c>
       <c r="K78" s="2">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="L78" s="2">
-        <v>2.97</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="M78" s="2">
-        <v>4.0199999999999996</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.2">
@@ -4294,125 +4297,125 @@
         <v>25</v>
       </c>
       <c r="C79" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D79" s="2">
-        <v>0.82</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="E79" s="3">
-        <f t="shared" si="4"/>
-        <v>0.57800000000000007</v>
+        <f>AVERAGE(I79:M79)</f>
+        <v>1.984</v>
       </c>
       <c r="F79" s="2">
-        <v>0.11</v>
+        <v>0.35</v>
       </c>
       <c r="G79" s="3">
-        <f t="shared" si="5"/>
-        <v>0.09</v>
+        <f>ROUND(STDEV(I79:M79)/SQRT(COUNT(I79:M79)),2)</f>
+        <v>0.27</v>
       </c>
       <c r="H79" s="2">
         <v>5</v>
       </c>
       <c r="I79" s="4">
-        <v>0.76</v>
+        <v>1.03</v>
       </c>
       <c r="J79" s="2">
-        <v>0.8</v>
+        <v>2.14</v>
       </c>
       <c r="K79" s="2">
-        <v>0.55000000000000004</v>
+        <v>2.09</v>
       </c>
       <c r="L79" s="2">
-        <v>0.4</v>
+        <v>2.69</v>
       </c>
       <c r="M79" s="2">
-        <v>0.38</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>16</v>
-      </c>
-      <c r="B80" t="s">
-        <v>25</v>
-      </c>
-      <c r="C80" t="s">
-        <v>5</v>
+      <c r="A80" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="D80" s="2">
-        <v>1.32</v>
+        <v>2.12</v>
       </c>
       <c r="E80" s="3">
-        <f t="shared" si="4"/>
-        <v>1.1559999999999999</v>
+        <f>AVERAGE(I80:M80)</f>
+        <v>2.2120000000000002</v>
       </c>
       <c r="F80" s="2">
-        <v>0.2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G80" s="3">
-        <f t="shared" si="5"/>
-        <v>0.15</v>
+        <f>ROUND(STDEV(I80:M80)/SQRT(COUNT(I80:M80)),2)</f>
+        <v>0.04</v>
       </c>
       <c r="H80" s="2">
         <v>5</v>
       </c>
       <c r="I80" s="4">
-        <v>1.39</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="J80" s="2">
-        <v>0.86</v>
+        <v>2.31</v>
       </c>
       <c r="K80" s="2">
-        <v>1.54</v>
+        <v>2.13</v>
       </c>
       <c r="L80" s="2">
-        <v>1.23</v>
+        <v>2.11</v>
       </c>
       <c r="M80" s="2">
-        <v>0.76</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B81" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C81" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D81" s="2">
-        <v>1.1299999999999999</v>
+        <v>1.68</v>
       </c>
       <c r="E81" s="3">
-        <f t="shared" si="4"/>
-        <v>0.83799999999999986</v>
+        <f>AVERAGE(I81:M81)</f>
+        <v>1.6600000000000001</v>
       </c>
       <c r="F81" s="2">
-        <v>0.13</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G81" s="3">
-        <f t="shared" si="5"/>
-        <v>0.11</v>
+        <f>ROUND(STDEV(I81:M81)/SQRT(COUNT(I81:M81)),2)</f>
+        <v>0.53</v>
       </c>
       <c r="H81" s="2">
         <v>5</v>
       </c>
       <c r="I81" s="4">
-        <v>0.79</v>
+        <v>0.44</v>
       </c>
       <c r="J81" s="2">
-        <v>1.24</v>
+        <v>0.64</v>
       </c>
       <c r="K81" s="2">
-        <v>0.59</v>
+        <v>3.38</v>
       </c>
       <c r="L81" s="2">
-        <v>0.8</v>
+        <v>2.08</v>
       </c>
       <c r="M81" s="2">
-        <v>0.77</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.2">
@@ -4420,133 +4423,133 @@
         <v>16</v>
       </c>
       <c r="B82" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C82" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D82" s="2">
-        <v>0.45</v>
+        <v>4.3</v>
       </c>
       <c r="E82" s="3">
-        <f t="shared" si="4"/>
-        <v>0.49199999999999999</v>
+        <f>AVERAGE(I82:M82)</f>
+        <v>3.9159999999999995</v>
       </c>
       <c r="F82" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>1.07</v>
       </c>
       <c r="G82" s="3">
-        <f t="shared" si="5"/>
-        <v>0.11</v>
+        <f>ROUND(STDEV(I82:M82)/SQRT(COUNT(I82:M82)),2)</f>
+        <v>0.85</v>
       </c>
       <c r="H82" s="2">
         <v>5</v>
       </c>
       <c r="I82" s="4">
-        <v>0.45</v>
+        <v>2.7</v>
       </c>
       <c r="J82" s="2">
-        <v>0.49</v>
+        <v>2.74</v>
       </c>
       <c r="K82" s="2">
-        <v>0.25</v>
+        <v>6.38</v>
       </c>
       <c r="L82" s="2">
-        <v>0.39</v>
+        <v>5.56</v>
       </c>
       <c r="M82" s="2">
-        <v>0.88</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B83" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C83" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D83" s="2">
-        <v>0.33</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="E83" s="3">
-        <f t="shared" si="4"/>
-        <v>0.378</v>
+        <f>AVERAGE(I83:M83)</f>
+        <v>5.42</v>
       </c>
       <c r="F83" s="2">
-        <v>0.09</v>
+        <v>0.72</v>
       </c>
       <c r="G83" s="3">
-        <f t="shared" si="5"/>
-        <v>7.0000000000000007E-2</v>
+        <f>ROUND(STDEV(I83:M83)/SQRT(COUNT(I83:M83)),2)</f>
+        <v>0.97</v>
       </c>
       <c r="H83" s="2">
         <v>5</v>
       </c>
       <c r="I83" s="4">
-        <v>0.22</v>
+        <v>4.37</v>
       </c>
       <c r="J83" s="2">
-        <v>0.32</v>
+        <v>7.03</v>
       </c>
       <c r="K83" s="2">
-        <v>0.57999999999999996</v>
+        <v>6</v>
       </c>
       <c r="L83" s="2">
-        <v>0.48</v>
+        <v>7.5</v>
       </c>
       <c r="M83" s="2">
-        <v>0.28999999999999998</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>16</v>
-      </c>
-      <c r="B84" t="s">
-        <v>25</v>
-      </c>
-      <c r="C84" t="s">
+      <c r="A84" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C84" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D84" s="2">
-        <v>3.76</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="E84" s="3">
-        <f t="shared" si="4"/>
-        <v>3.7739999999999996</v>
+        <f>AVERAGE(I84:M84)</f>
+        <v>3.9480000000000004</v>
       </c>
       <c r="F84" s="2">
-        <v>0.4</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G84" s="3">
-        <f t="shared" si="5"/>
-        <v>0.25</v>
+        <f>ROUND(STDEV(I84:M84)/SQRT(COUNT(I84:M84)),2)</f>
+        <v>0.11</v>
       </c>
       <c r="H84" s="2">
         <v>5</v>
       </c>
       <c r="I84" s="4">
-        <v>4.3899999999999997</v>
+        <v>4.01</v>
       </c>
       <c r="J84" s="2">
-        <v>4.03</v>
+        <v>3.67</v>
       </c>
       <c r="K84" s="2">
-        <v>2.99</v>
+        <v>3.71</v>
       </c>
       <c r="L84" s="2">
-        <v>3.45</v>
+        <v>4.08</v>
       </c>
       <c r="M84" s="2">
-        <v>4.01</v>
+        <v>4.2699999999999996</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B85" t="s">
         <v>25</v>
@@ -4555,36 +4558,36 @@
         <v>6</v>
       </c>
       <c r="D85" s="2">
-        <v>2.0299999999999998</v>
+        <v>3.76</v>
       </c>
       <c r="E85" s="3">
-        <f t="shared" si="4"/>
-        <v>1.984</v>
+        <f>AVERAGE(I85:M85)</f>
+        <v>3.7739999999999996</v>
       </c>
       <c r="F85" s="2">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="G85" s="3">
-        <f t="shared" si="5"/>
-        <v>0.27</v>
+        <f>ROUND(STDEV(I85:M85)/SQRT(COUNT(I85:M85)),2)</f>
+        <v>0.25</v>
       </c>
       <c r="H85" s="2">
         <v>5</v>
       </c>
       <c r="I85" s="4">
-        <v>1.03</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="J85" s="2">
-        <v>2.14</v>
+        <v>4.03</v>
       </c>
       <c r="K85" s="2">
-        <v>2.09</v>
+        <v>2.99</v>
       </c>
       <c r="L85" s="2">
-        <v>2.69</v>
+        <v>3.45</v>
       </c>
       <c r="M85" s="2">
-        <v>1.97</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.2">
@@ -6493,34 +6496,34 @@
       </c>
       <c r="F34" s="4">
         <f ca="1">ROUND(AVERAGE(I34:M34),2)</f>
-        <v>9.34</v>
+        <v>10.55</v>
       </c>
       <c r="G34" s="2">
         <f ca="1">ROUND(STDEV(I34:M34)/SQRT(COUNT(I34:M34)),2)</f>
-        <v>2.98</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="H34" s="2">
         <v>5</v>
       </c>
       <c r="I34" s="4">
         <f ca="1">ABS(ROUND($D34 + (_xlfn.NORM.INV(RAND(), 0, 1) * ($E34*SQRT($H34))),2))</f>
-        <v>8.89</v>
+        <v>5.91</v>
       </c>
       <c r="J34" s="2">
         <f ca="1">ABS(ROUND($D34 + (_xlfn.NORM.INV(RAND(), 0, 1) * ($E34*SQRT($H34))),2))</f>
-        <v>8.83</v>
+        <v>4.87</v>
       </c>
       <c r="K34" s="2">
         <f ca="1">ABS(ROUND($D34 + (_xlfn.NORM.INV(RAND(), 0, 1) * ($E34*SQRT($H34))),2))</f>
-        <v>4.91</v>
+        <v>15.32</v>
       </c>
       <c r="L34" s="2">
         <f ca="1">ABS(ROUND($D34 + (_xlfn.NORM.INV(RAND(), 0, 1) * ($E34*SQRT($H34))),2))</f>
-        <v>3.57</v>
+        <v>17.350000000000001</v>
       </c>
       <c r="M34" s="2">
         <f ca="1">ABS(ROUND($D34 + (_xlfn.NORM.INV(RAND(), 0, 1) * ($E34*SQRT($H34))),2))</f>
-        <v>20.5</v>
+        <v>9.2899999999999991</v>
       </c>
     </row>
   </sheetData>
@@ -6546,7 +6549,7 @@
       </c>
       <c r="B1">
         <f ca="1">ROUND($A$1 + (_xlfn.NORM.INV(RAND(), 0, 1) * $A$4),2)</f>
-        <v>1.1000000000000001</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -6555,7 +6558,7 @@
       </c>
       <c r="B2">
         <f t="shared" ref="B2:B5" ca="1" si="0">ROUND($A$1 + (_xlfn.NORM.INV(RAND(), 0, 1) * $A$4),2)</f>
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -6570,15 +6573,15 @@
       </c>
       <c r="B3">
         <f t="shared" ca="1" si="0"/>
-        <v>0.55000000000000004</v>
+        <v>0.83</v>
       </c>
       <c r="D3">
         <f ca="1">AVERAGE(B1:B5)</f>
-        <v>0.91799999999999993</v>
+        <v>1.3119999999999998</v>
       </c>
       <c r="E3">
         <f ca="1">STDEV(B1:B5)/SQRT(A3)</f>
-        <v>0.1025377979088687</v>
+        <v>0.18095303258028061</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -6588,13 +6591,13 @@
       </c>
       <c r="B4">
         <f t="shared" ca="1" si="0"/>
-        <v>1.07</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B5">
         <f t="shared" ca="1" si="0"/>
-        <v>0.84</v>
+        <v>1.05</v>
       </c>
     </row>
   </sheetData>
